--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -2,13 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$159</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -28,7 +32,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -44,12 +48,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002D5016"/>
-        <bgColor rgb="002D5016"/>
+        <fgColor rgb="00355E3B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -57,35 +60,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -446,21 +435,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
@@ -505,32 +494,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Angel Wings</t>
+          <t>Japanese Maple 'Bloodgood'</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Senecio candicans</t>
+          <t>Acer palmatum 'Bloodgood'</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Full sun</t>
+          <t>Dappled shade to partial sun. Sheltered from harsh afternoon sun.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Well-drained soil; drought-tolerant.</t>
+          <t>Keep soil consistently moist but never waterlogged.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Avoid getting water on the velvety leaves. Protect from hard frosts.</t>
+          <t>Slightly acidic, well-drained loam. Mulch in spring; minimal pruning.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Evergreen in mild areas. Offers stunning silver foliage mostly spring to autumn.</t>
+          <t>Deep red-purple leaves open in April, hold their colour through summer and brighten to fiery red in autumn; bare and architectural in winter.</t>
         </is>
       </c>
     </row>
@@ -542,32 +531,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Astilbe</t>
+          <t>Japanese Aralia</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Astilbe</t>
+          <t>Fatsia japonica 'Spider's Web'</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Partial to full shade</t>
+          <t>Shade to partial shade. Tolerates deep shade.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Moist to wet soil; do not let dry out.</t>
+          <t>Moderate; let top inch dry between waterings.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Leave dried flower heads for winter interest or cut back in autumn.</t>
+          <t>Rich, well-drained soil. Cut back leggy stems in spring.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Herbaceous perennial. Dies back in winter. Feathery flower plumes appear in summer.</t>
+          <t>Evergreen with cream-flecked leaves; cream globe flowers October–November.</t>
         </is>
       </c>
     </row>
@@ -579,32 +568,32 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Box Hedging</t>
+          <t>Rhododendron</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Buxus sempervirens</t>
+          <t>Rhododendron 'Goldflimmer'</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Full sun to full shade.</t>
+          <t>Partial shade. Avoid hot, dry sun.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tolerates most well-drained soils. Water regularly when newly planted; established plants are fairly drought-tolerant.</t>
+          <t>Even moisture; never waterlogged.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Clip twice a year (late spring and late summer) to maintain a neat shape. Watch for box blight and box tree caterpillar.</t>
+          <t>Acidic, ericaceous soil. Mulch with leaf mould; deadhead spent flowers.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Evergreen. Retains dense, glossy green foliage year-round. Produces small insignificant flowers in spring.</t>
+          <t>Evergreen golden-variegated leaves year-round; lavender-purple flowers May.</t>
         </is>
       </c>
     </row>
@@ -616,32 +605,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>English Daisy</t>
+          <t>Hosta 'Patriot'</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Bellis perennis</t>
+          <t>Hosta 'Patriot'</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade.</t>
+          <t>Shade to partial shade.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Moist, well-drained soil. Water regularly.</t>
+          <t>Keep soil moist; mulch to retain moisture.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent flowers to encourage continued blooming. Can self-seed freely.</t>
+          <t>Watch for slugs and snails. Divide clumps every few years.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Short-lived perennial often grown as a biennial. Produces pink, red, or white pom-pom flowers from early spring through summer. May die back in hot summers.</t>
+          <t>Foliage emerges April; lilac flowers July; dies back in autumn.</t>
         </is>
       </c>
     </row>
@@ -653,32 +642,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Euonymus</t>
+          <t>Box Hedging</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Euonymus fortunei (golden variety)</t>
+          <t>Buxus sempervirens</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade.</t>
+          <t>Sun or partial shade.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tolerates most soils; average watering.</t>
+          <t>Moderate; established plants tolerate dry spells.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Prune in spring to maintain shape. Can be used as ground cover or trained upwards.</t>
+          <t>Clip twice yearly (May and August). Watch for box blight.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Evergreen. Keeps its bright golden-variegated foliage all year round. Colours may intensify in full sun.</t>
+          <t>Evergreen year-round.</t>
         </is>
       </c>
     </row>
@@ -690,32 +679,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Hosta (Plantain Lily)</t>
+          <t>Euonymus 'Emerald 'n' Gold'</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Euonymus fortunei 'Emerald 'n' Gold'</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Partial to full shade</t>
+          <t>Sun or partial shade.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Rich moist soil.</t>
+          <t>Moderate; very tolerant once established.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Watch out for slugs and snails!</t>
+          <t>Trim to shape in spring. Tough and trouble-free.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Herbaceous perennial. Dies back underground in winter. Lush leaves emerge in spring.</t>
+          <t>Golden-variegated evergreen; pink tints in cold weather.</t>
         </is>
       </c>
     </row>
@@ -727,32 +716,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Japanese Aralia</t>
+          <t>Dahlia 'Double Dreamy Lilac'</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Fatsia japonica 'Spider''s Web'</t>
+          <t>Dahlia Double Dreamy Lilac (best-fit identification)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Partial to full shade</t>
+          <t>Full sun. Needs warmth to thrive.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Moist well-drained soil.</t>
+          <t>Regular watering, especially in dry spells. Don't let soil dry out completely.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Protect from harsh cold winds.</t>
+          <t>Rich, well-drained soil. Mulch the crown and support only if the compact stems lean under their flowers. Lift tubers in autumn or mulch heavily for winter protection. Pinch early and deadhead for continuous blooming.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Evergreen. Keeps its speckled tropical leaves year-round.</t>
+          <t>Dark bronze-black foliage from May; fully double lilac-magenta flowers July–October; dies back after the first hard frost. Tubers overwinter with protection.</t>
         </is>
       </c>
     </row>
@@ -764,32 +753,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Japanese Maple</t>
+          <t>Dahlia 'Double Dreamy Gold'</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Acer palmatum</t>
+          <t>Dahlia Double Dreamy Gold (best-fit identification)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Dappled shade to partial sun.</t>
+          <t>Full sun. Needs warmth to thrive.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Keep soil consistently moist but not waterlogged.</t>
+          <t>Regular watering, especially in dry spells. Don't let soil dry out completely.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Slightly acidic, well-drained loam.</t>
+          <t>Rich, well-drained soil. Mulch the crown and support only if the compact stems lean under their flowers. Lift tubers in autumn or mulch heavily for winter protection. Pinch early and deadhead for continuous blooming.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Requires minimal pruning. Remove dead or crossing branches during the dormant winter season.</t>
+          <t>Dark bronze-black foliage from May; fully double golden-yellow flowers July–October; dies back after the first hard frost. Tubers overwinter with protection.</t>
         </is>
       </c>
     </row>
@@ -801,143 +790,143 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron</t>
+          <t>Hosta (gold)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Goldflimmer'</t>
+          <t>Hosta 'Gold Standard'</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Partial shade</t>
+          <t>Shade to partial shade.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Acidic (ericaceous) moist well-drained soil.</t>
+          <t>Keep moist.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Deadhead carefully after flowering. Needs ericaceous compost/fertiliser.</t>
+          <t>Slug protection; divide every few years.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Evergreen. Keeps its variegated leaves all year. Blooms with purple flowers in late spring.</t>
+          <t>Emerges April; lilac flowers July.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Bed 2</t>
+          <t>Bed 1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Angel Wings</t>
+          <t>Little Heath</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Senecio candicans</t>
+          <t>Pieris japonica 'Little Heath'</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Full sun</t>
+          <t>Partial shade, sheltered from cold drying winds. Tolerates sun if the soil stays moist.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Well-drained soil; drought-tolerant.</t>
+          <t>Keep evenly moist, especially while establishing. Do not allow the root ball to dry out or sit waterlogged.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Avoid getting water on the velvety leaves. Protect from hard frosts.</t>
+          <t>Grow in humus-rich, acidic soil or ericaceous compost. Mulch with leaf mould or composted bark. Remove faded flowers and damaged growth only; little routine pruning is needed.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Evergreen in mild areas. Offers stunning silver foliage mostly spring to autumn.</t>
+          <t>Cream-edged evergreen foliage year-round; red young shoots and white spring flowers, usually March–May.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Bed 2</t>
+          <t>Bed 1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Forget-me-not</t>
+          <t>Abelia 'Kaleidoscope'</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Myosotis</t>
+          <t>Abelia × grandiflora 'Kaleidoscope'</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Partial shade.</t>
+          <t>Full sun to partial shade; the foliage colours best with good light.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Keep soil consistently moist.</t>
+          <t>Moderate while establishing; avoid waterlogged soil.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Humus-rich, moisture-retentive soil.</t>
+          <t>Lightly trim after flowering only if needed. Shelter from cold drying wind and mulch over moist soil.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Pull up plants after flowering to prevent excessive self-seeding, or leave them if naturalising is desired.</t>
+          <t>Yellow-and-green foliage warms to orange-red; fragrant white flowers continue into autumn.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Bed 2</t>
+          <t>Bed 1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Hosta (Plantain Lily)</t>
+          <t>Pieris 'Forest Flame'</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Pieris 'Forest Flame'</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Partial to full shade</t>
+          <t>Partial shade or sheltered sun; protect new growth from early frost and harsh morning sun.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Rich moist soil.</t>
+          <t>Keep evenly moist but well drained; use rainwater where practical.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Watch out for slugs and snails!</t>
+          <t>Grow in acidic, humus-rich soil. Mulch with leaf mould or composted bark and prune only damaged growth.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Herbaceous perennial. Dies back underground in winter. Lush leaves emerge in spring.</t>
+          <t>Evergreen foliage opens vivid red, softens through pink and cream, then matures green; cream spring flowers.</t>
         </is>
       </c>
     </row>
@@ -949,32 +938,32 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Maiden Pink</t>
+          <t>Peony</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dianthus deltoides</t>
+          <t>Paeonia lactiflora</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Full sun</t>
+          <t>Full sun, sheltered.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Well-drained neutral to alkaline soil.</t>
+          <t>Moderate; deep watering when budding.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Deadhead regularly to prolong flowering.</t>
+          <t>Don't bury the crown. Stake floppy heads. Resents being moved.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Evergreen mat of foliage. Blooms with bright pink/red flowers in summer.</t>
+          <t>Huge fragrant flowers May–June; foliage to ground in autumn.</t>
         </is>
       </c>
     </row>
@@ -986,32 +975,32 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Nemesia</t>
+          <t>Weigela</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nemesiaspp.</t>
+          <t>Weigela florida</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Regular; keep the soil moist but ensure it does not become soggy.</t>
+          <t>Moderate.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Rich, well-drained compost or soil.</t>
+          <t>Prune one in three old stems after flowering.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Trim the plant back slightly after the initial flush of flowers to encourage a second display.</t>
+          <t>Pink trumpet flowers May–June; sometimes a second flush.</t>
         </is>
       </c>
     </row>
@@ -1023,32 +1012,32 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Peony</t>
+          <t>Silverbush</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Paeonia lactiflora</t>
+          <t>Convolvulus cneorum</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light shade</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Rich well-drained soil; moderate watering.</t>
+          <t>Drought-tolerant. Hates wet feet.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Provide plant supports for heavy flower heads. Cut back dead foliage in late autumn.</t>
+          <t>Sharp drainage essential. Light trim after flowering.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Herbaceous perennial. Dies back completely in winter. Huge blooms in late spring/early summer.</t>
+          <t>White trumpet flowers May–September on silver mound.</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1049,32 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Silverbush</t>
+          <t>Avens</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Convolvulus cneorum</t>
+          <t>Geum</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Full sun</t>
+          <t>Sun or partial shade.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Very well-drained soil; drought-tolerant.</t>
+          <t>Moderate.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe winter wet and cold.</t>
+          <t>Deadhead to encourage a second flush. Divide clumps every few years.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Evergreen. Retains silver foliage year-round. Produces white/pink flowers in spring and summer.</t>
+          <t>Orange flowers May–July, often a second flush in late summer.</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1086,32 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Variegated Dogwood</t>
+          <t>Maiden Pink</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cornus alba</t>
+          <t>Dianthus deltoides 'Leuchtfunk'</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Tolerates most soils even damp ones.</t>
+          <t>Low; sharp drainage.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Prune hard (coppice) in late winter/early spring to encourage bright new stems.</t>
+          <t>Trim after flowering. Mat-forming.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Deciduous. Drops leaves in autumn to reveal striking bright red winter stems.</t>
+          <t>Pink stars June–August.</t>
         </is>
       </c>
     </row>
@@ -1134,32 +1123,32 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Weeping Cherry</t>
+          <t>Hydrangea petiolaris</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Prunus species</t>
+          <t>Hydrangea anomala subsp. petiolaris</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to full shade. Tolerates north-facing walls.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Needs moderately fertile, well-drained soil. Keep the ground consistently moist but avoid waterlogged conditions.</t>
+          <t>Moist but well-drained.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Prune during the dormant winter period only to remove dead, diseased, or crossing branches. Avoid disrupting the natural weeping form. Apply a balanced fertiliser in early spring.</t>
+          <t>Slow to establish; once settled it is vigorous. Light prune to shape after flowering.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Deciduous. Exhibits prolific spring blossoms before or alongside leaf emergence. The canopy provides summer shade before leaves turn yellow or bronze and drop in autumn.</t>
+          <t>White lace-cap flowers June–July; golden autumn leaf colour; interesting bark in winter.</t>
         </is>
       </c>
     </row>
@@ -1171,106 +1160,106 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Weigela</t>
+          <t>Euonymus 'Emerald Gaiety'</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Weigela florida</t>
+          <t>Euonymus fortunei 'Emerald Gaiety'</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade</t>
+          <t>Sun or partial shade.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Moist well-drained soil.</t>
+          <t>Moderate; tolerates dry spells once established.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Prune immediately after flowering.</t>
+          <t>Trim to shape in spring. Very hardy and low-maintenance. Moved from Bed 3, June 2026.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Deciduous. Drops leaves in autumn. Blooms with trumpet flowers in late spring/early summer.</t>
+          <t>Evergreen white-margined leaves year-round; pink blush to the margins in cold spells.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Bed 3</t>
+          <t>Bed 2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Apple Tree</t>
+          <t>Rose (inherited)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Malus domestica</t>
+          <t>Rosa (cultivar unknown)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Best in full sun; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Regular watering, particularly during fruit development.</t>
+          <t>Water deeply during sustained dry spells, checking the soil first.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Well-drained, fertile soil.</t>
+          <t>Mulch and feed in spring. Deadhead if it repeats and delay class-specific pruning until its growth habit is documented.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Prune in late winter while dormant to maintain structure and encourage fruiting spurs.</t>
+          <t>Summer flowers; repeat pattern and hip production still to be recorded.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Bed 3</t>
+          <t>Bed 2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Avens</t>
+          <t>Butterfly Bush</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Geum</t>
+          <t>Buddleja (species unknown)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade</t>
+          <t>Full sun for the strongest flowering.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Moist but well-drained soil; water regularly.</t>
+          <t>Low to moderate once established; water deeply during prolonged drought.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent flowers to encourage more blooms.</t>
+          <t>Deadhead after flowering. Confirm the species before choosing a hard- or light-pruning regime.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Herbaceous or semi-evergreen. Produces bright flowers from late spring through summer.</t>
+          <t>Fragrant summer flower panicles attract butterflies and other pollinators.</t>
         </is>
       </c>
     </row>
@@ -1282,49 +1271,49 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Wintercreeper</t>
+          <t>Kerria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Euonymus fortunei</t>
+          <t>Kerria japonica</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Full sun to full shade</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tolerates most soils; average watering.</t>
+          <t>Low to moderate. Tolerates dry shade.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Prune in spring to maintain shape.</t>
+          <t>Cut flowered stems back to the base after flowering. Remove all-green suckers promptly.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Evergreen shrub. Keeps its bright variegated foliage all year round.</t>
+          <t>Bright single yellow flowers April–May; arching green stems attractive all year.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Bed 4</t>
+          <t>Bed 3</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Centaurea 'Snowy Owl'</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Lavandula angustifolia</t>
+          <t>Centaurea montana 'Snowy Owl'</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1334,34 +1323,34 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Well-drained, poor to moderately fertile soil. Drought-tolerant once established.</t>
+          <t>Low to moderate.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Prune after flowering in late summer, cutting back to just above the woody growth. Do not cut into old wood.</t>
+          <t>Cut back after flowering for a second flush. Short-lived perennial; divide every 2–3 years.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Evergreen. Grey-green aromatic foliage year-round. Produces fragrant purple flower spikes from mid to late summer. Attractive to bees and butterflies.</t>
+          <t>White cornflower blooms May–July; ferny silver-green foliage.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Bed 4</t>
+          <t>Bed 3</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>New Zealand Flax</t>
+          <t>Spiraea 'Double Play Big Bang'</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Phormium</t>
+          <t>Spiraea japonica 'Double Play Big Bang'</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1371,71 +1360,71 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Moderate; keep evenly moist during the growing season.</t>
+          <t>Moderate. Water well until established; tolerates dry spells after.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Versatile; prefers well-drained conditions.</t>
+          <t>Prune hard in early spring to encourage bright new foliage and flowers. Remove spent flower heads. Hardy shrub.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Cut back old, damaged, or untidy leaves right to the base in spring.</t>
+          <t>Vivid orange-red new growth in spring; bright pink flowers June–August; foliage turns orange-red in autumn.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Bed 4</t>
+          <t>Bed 3</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sedum 'Rose Carpet'</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>Sedum pluricaule 'Rose Carpet'</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Regular, deep watering at the base to avoid wetting the foliage.</t>
+          <t>Low once established; allow the soil surface to dry and avoid winter saturation.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Rich, well-drained, slightly acidic loam.</t>
+          <t>Keep in sharply drained neutral to alkaline soil. Cut back after flowering and divide in spring if needed.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Prune hard in late winter or early spring. Deadhead spent blooms regularly to encourage further flowering.</t>
+          <t>Grey-green succulent leaves and dense rose-pink flower clusters in late summer; dormant in winter.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Bed 4</t>
+          <t>Bed 3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Wisteria</t>
+          <t>Weeping Cherry</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Wisteriaspp.</t>
+          <t>Prunus species</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1445,145 +1434,145 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Regular watering until a deep root system is established.</t>
+          <t>Moderate; deep watering when young.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Well-drained, fertile soil.</t>
+          <t>Light pruning after flowering; avoid heavy cuts.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Requires bi-annual pruning (summer and winter) to control vigorous growth and promote flower buds.</t>
+          <t>Pink blossom April; green canopy summer; bare winter.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Bed 4</t>
+          <t>Bed 3</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Yucca</t>
+          <t>Rose (inherited)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Yucca filamentosa</t>
+          <t>Rosa (cultivar unknown)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Best in full sun; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Very well-drained soil; highly drought-tolerant once established.</t>
+          <t>Water deeply during sustained dry spells, checking the soil first.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Low maintenance. Remove dead or damaged leaves at the base. Wear gloves as leaf tips can be sharp.</t>
+          <t>Mulch and feed in spring. Deadhead if it repeats and delay class-specific pruning until its growth habit is documented.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Evergreen. Spiky architectural rosettes provide year-round structure. Produces tall spikes of creamy-white bell flowers in summer.</t>
+          <t>Yellow summer flowers and developing buds photographed in August; repeat pattern and hip production still to be recorded.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 3</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Aubrieta (Rock Cress)</t>
+          <t>Evergreen Candytuft — assumed</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Aubrieta deltoidea</t>
+          <t>Iberis sempervirens (assumed)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Full sun</t>
+          <t>Full sun for compact growth and reliable flowering.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Well-drained soil; drought-tolerant once established.</t>
+          <t>Low once established; avoid stagnant winter moisture.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Shear back after blooming to keep it compact.</t>
+          <t>Grow in sharply drained soil. Trim lightly after flowering to keep the evergreen mound compact; retain the assumed qualification until flowers or a label confirm it.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage. Bursts with purple flowers in spring.</t>
+          <t>Evergreen narrow foliage with white spring flowers expected if the provisional identification is correct.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 3</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Cabbage Tree</t>
+          <t>Variegated Lesser Periwinkle — assumed</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Cordyline australis</t>
+          <t>Vinca minor (variegated cultivar; assumed)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade.</t>
+          <t>Partial shade to shade; tolerates sun where soil stays moist.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Moderate; drought-tolerant when mature.</t>
+          <t>Low to moderate once established; water in prolonged drought.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Adaptable, but requires good drainage.</t>
+          <t>Trim spreading stems where they cross paths or smother neighbours. Keep the cultivar unresolved until flowers, leaf detail or a label provide stronger evidence.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Remove dead or yellowing leaves from the base of the tufts to maintain a tidy appearance.</t>
+          <t>Evergreen cream-edged foliage; violet-blue spring flowers expected if the provisional identification is correct.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Honeysuckle</t>
+          <t>Apple Tree</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Lonicera</t>
+          <t>Malus domestica</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1593,182 +1582,182 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Adaptable to various soil types, provided they are moist and well-drained. Water regularly during the first growing season.</t>
+          <t>Deep watering in dry spells, especially when fruiting.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Prune after flowering to control growth and remove congested stems. Train new shoots along supports as required.</t>
+          <t>Winter prune for shape. Thin fruit in June for size.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Deciduous or semi-evergreen depending on the exact species. Characterised by rapid summer growth and fragrant tubular flowers, often followed by small berries in autumn.</t>
+          <t>Blossom April; fruit August–October; bare winter.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 4</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Houseleeks (Hens and Chicks)</t>
+          <t>Callistemon Inferno ('Yanferno')</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum</t>
+          <t>Callistemon Inferno ('Yanferno')</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Full sun</t>
+          <t>Full sun. Thrives in a warm, sheltered spot.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Highly well-drained/gritty soil; water sparingly.</t>
+          <t>Moderate. Drought-tolerant once established. Good drainage essential.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Very low maintenance. Remove dead rosettes after they flower and die.</t>
+          <t>RHS hardiness H3 (about −5°C to 1°C). Keep in a warm, sheltered position and protect thoroughly from severe cold and winter winds. Prune only in summer immediately after flowering, removing a little older growth at a time.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Evergreen rosettes. Forms offsets (chicks) during growing season.</t>
+          <t>Evergreen; vivid red bottlebrush flowers June–August, sometimes a repeat flush in autumn. Architectural foliage year-round.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 4</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>New Zealand Flax (dark)</t>
+          <t>Gaillardia</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Phormium 'Platt's Black' or similar</t>
+          <t>Gaillardia × grandiflora</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Moderate; keep evenly moist during the growing season. Versatile; prefers well-drained conditions.</t>
+          <t>Low to moderate. Sharp drainage essential — hates wet feet.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Cut back old, damaged, or untidy leaves right to the base in spring. Protect crown from severe frost with mulch.</t>
+          <t>Deadhead regularly for near-continuous bloom. Cut back hard in autumn. Short-lived perennial — may need replacing every 2–3 years.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Evergreen. Dark burgundy-black sword-shaped leaves provide dramatic year-round contrast against the grey slate chippings.</t>
+          <t>Vivid red, orange and yellow daisy-like flowers June–October; near-continuous if deadheaded.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 4</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Rosemary</t>
+          <t>Abelia 'Kaleidoscope'</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Salvia rosmarinus</t>
+          <t>Abelia × grandiflora 'Kaleidoscope'</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade. Best foliage colour in full sun.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Low; highly drought-tolerant once established. Allow soil to dry between waterings.</t>
+          <t>Moderate. Good drainage.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Poor to moderately fertile, very well-drained soil.</t>
+          <t>Light trim after flowering to maintain shape. Very low maintenance. Semi-evergreen — may drop some leaves in a hard winter but recovers readily.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Prune lightly after flowering to maintain shape and prevent the centre from becoming overly woody.</t>
+          <t>Variegated yellow and green leaves spring–summer, turning orange-red in autumn; small white fragrant flowers July–September. Semi-evergreen.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 4</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Stonecrop</t>
+          <t>Lobelia 'Starship Scarlet Bronze Leaf'</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Sedum (various trailing types)</t>
+          <t>Lobelia × speciosa 'Starship Scarlet Bronze Leaf'</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Full sun</t>
+          <t>Full sun to partial shade. Best flowering with at least half a day of sun.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Well-drained soil; very drought-tolerant.</t>
+          <t>Keep evenly moist; do not allow the compost to dry out in summer.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Low maintenance. Trim back if it gets too leggy.</t>
+          <t>Keep evenly moist while it establishes. Deadhead spent spikes; mulch the crown for winter and avoid stagnant soil.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Mostly evergreen. Flowers in summer. Leaf colours may deepen in cooler weather.</t>
+          <t>Bronze foliage from spring; tall scarlet flower spikes July–September; dies back in winter and returns from the crown.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Patio</t>
+          <t>Bed 5</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Clematis</t>
+          <t>Wisteria</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Clematis (likely montana)</t>
+          <t>Wisteria spp.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1778,58 +1767,4574 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Requires moist, well-drained earth. Deep watering is necessary during extended dry spells.</t>
+          <t>Deep watering when young; established plants tolerate drought.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Pruning depends on the specific group; spring-flowering types generally need minimal pruning immediately after flowering to control size. Mulch around the base to keep roots cool.</t>
+          <t>Prune twice yearly: August (long shoots to 6 leaves) and February (back to 2–3 buds).</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Deciduous. Produces vigorous growth and abundant flowers in spring. Foliage drops in autumn, leaving bare woody stems over winter.</t>
+          <t>Lilac racemes May; bare gnarled stems winter.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Deep watering, mulch in spring.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Prune in late winter. Feed in spring and after first flush.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Flowers June–September; bare winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand Flax (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Phormium (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; shelter from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Moderate while establishing; drought-tolerant later, but avoid prolonged waterlogging.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Grow in fertile, well-drained soil. Remove damaged leaves at the base in spring and mulch the crown before hard frost. Cultivar still needs confirmation from a label or diagnostic photos.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen sword-shaped foliage year-round; mature plants may produce tall flower stems in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Alstroemeria</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Alstroemeria hybrid</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; flowering is strongest with plenty of light.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist in the growing season, but never waterlogged.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Feed weekly while flowering. Pull spent flower stems cleanly from the base rather than cutting them. Protect the pot from hard frost in winter.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Red-and-gold flowers from summer into autumn above dark foliage; dies back in cold weather.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Petunia 'Bee's Knees'</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Petunia 'Bee's Knees'</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for the most flowers; tolerates light partial shade.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Water when the top of the compost begins to dry; pots may need daily checks in hot weather.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Feed weekly with a high-potash liquid feed and deadhead or trim leggy growth to keep flowers coming.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Clear yellow flowers from summer until the first frost; grown as a tender annual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Sun to shade; the yellow-and-green foliage colours best in bright indirect light or partial shade.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let the surface dry slightly between waterings, without letting the pot dry out completely.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Trim trailing stems to shape. Hardy and evergreen, but vigorous if later planted into open ground.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Golden variegated foliage year-round with small violet-blue flowers mainly in spring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Nemesia</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nemesia hybrid</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade; a little afternoon shade helps during hot spells.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Keep the compost evenly moist but not waterlogged; check the pot frequently in warm or windy weather.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Feed fortnightly while flowering. Deadhead or trim back tired stems by about a third to encourage a fresh flush.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Small, scented flowers from summer into autumn; usually grown as tender seasonal colour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Lythrum 'Robin'</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Lythrum salicaria 'Robin'</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; flowers best in full sun.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Moisture-loving. Keep the compost consistently moist, especially during flowering.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead to prolong flowering or leave some seedheads for wildlife. Cut old stems down in late winter or early spring.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Dense magenta flower spikes in summer, popular with bees; herbaceous and dormant in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Begonia 'Carmen'</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Begonia 'Carmen'</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Bright partial shade or gentle morning sun; protect from harsh midday sun.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist but not saturated. Water the compost rather than the leaves and flowers.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead faded blooms and feed fortnightly in summer. Tender — protect from frost and overwinter under cover if keeping it.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Double red flowers through summer and early autumn; tender and dormant or discarded after frost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Nemesia 'Aroma Heart of Gold'</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nemesia Aroma Heart of Gold (Aroma Series)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade in a sheltered position.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Keep moist but well drained, watering in dry spells to maintain flowering.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Pinch the growing tips for a bushy plant. Trim flowering shoots after the first flush to encourage more blooms; protect cuttings from frost if overwintering.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Sweetly fragrant burgundy-red and creamy-yellow flowers with burnt-orange centres from summer into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Bed 5</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Cabbage Tree</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Cordyline australis 'Red Star'</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Moderate; established plants tolerate drought.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Tie up leaves in winter to protect crown if hard frost forecast.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen burgundy fountain of leaves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Houseleeks</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Sempervivum</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Very low. Hates wet.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Sharp drainage; almost no maintenance.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen rosettes; flowering rosettes die after blooming, replaced by offsets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Echeveria</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Echeveria cultivar</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Full sun or very bright light; acclimatise gradually to strong sun.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Low. Water only when the soil has dried; keep almost dry in winter.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Sharply drained soil. Tender: lift before frost and overwinter frost-free under cover.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen powdery grey-purple rosette; pink-red flower stems may appear in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Sedum 'Chocolate Ball'</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Sedum polytrichoides 'Chocolate Ball'</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Very low; let the gritty soil dry between waterings.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Sharp drainage is essential. RHS H3: protect from severe frost and prolonged winter wet.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen bronze-brown foliage; small yellow flowers in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Older Caucasian Stonecrop</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Phedimus spurius cultivar</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for compact growth and strongest colour.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Low; water only during establishment or prolonged drought.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Trim spent flower stems and pull wandering shoots back from smaller alpines. Keep the crown sharply drained.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Scalloped green leaves flush red; pink-red flower clusters age to brown seedheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Common Houseleek</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Sempervivum tectorum</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Very low; established rosettes normally need no extra water.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Keep grit around the crowns, clear trapped leaves and remove a parent rosette only after it flowers and dies naturally.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen rosettes colour more strongly in cold or bright conditions; starry flowers may appear in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Six-rowed Stonecrop</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Sedum sexangulare</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Very low once rooted.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Use gritty, lean soil and trim spreading stems where they crowd slower alpines.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen cylindrical leaves in six neat ranks; yellow star flowers in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Ajuga 'Fancy Finch'</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Ajuga 'Fanfin' (Feathered Friends Fancy Finch)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade; protect the golden foliage from scorching midday sun.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Keep evenly moist while establishing.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Trim spent flower spikes and remove runners that stray into the driest succulent pockets.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Golden to orange narrow foliage year-round; blue flower spikes in spring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Hydrangea 'Snowflake'</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Hydrangea quercifolia 'Brido' (Snowflake)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; afternoon shade is useful in hot weather.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Moderate to high while establishing; soak deeply during dry spells.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Give it a humus-rich pocket beneath the gravel, mulch clear of the crown and prune only dead or misplaced wood after flowering.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Double white flower panicles fade pink; oak-shaped leaves turn rich red and purple in autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Chick Charms Houseleek Mix</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Sempervivum Chick Charms Series</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Very low; only newly planted offsets need occasional water.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>The label confirms the series but not its individual cultivars. Keep crowns dry and remove spent flowering rosettes.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen rosettes change colour with season and temperature; mature rosettes may flower in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Achillea 'King Alfred'</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Achillea 'King Alfred'</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Low once established.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Keep in lean, sharply drained soil and trim untidy growth in spring.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Low grey-green aromatic mat with pale yellow flower heads in late spring and early summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Golden Stonecrop 'Aureum'</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Sedum acre 'Aureum'</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Very low.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Avoid rich soil and trim after flowering if it spreads over slower plants.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen yellow-gold foliage with small yellow flowers in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Cobweb Houseleek</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Sempervivum arachnoideum</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Very low.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Keep winter rain and leaf litter out of the rosettes; detach offsets to extend the colony.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen cobwebbed rosettes, often red-flushed; pink star flowers in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Thrift 'Armada White'</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Armeria maritima 'Armada White'</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Low to moderate while establishing; drought tolerant later.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead the white globes and keep the crown clear in gritty soil.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen grassy cushions with white flower heads from spring into summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Houseleek 'Purple Quartz'</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Sempervivum 'Purple Quartz' (Big Sam Series)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Very low.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Provide sharp drainage, clear debris and protect from persistent winter wet rather than cold.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Grey-green rosettes flush pink and purple; mature rosettes flower once before offsets replace them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Sedum 'Angelina'</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Sedum rupestre 'Angelina'</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for strongest gold and orange colour.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Very low once established.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Shear or pull back spreading shoots when they overrun small rosettes.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Golden needle-like foliage turns orange in cold weather; yellow flowers in summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Stonecrop 'Dragon's Blood'</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Phedimus spurius 'Schorbuser Blut'</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Low once established.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Trim spent heads and keep spreading stems within their allotted gravel pocket.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Green-red scalloped leaves deepen burgundy; clusters of deep pink-red summer flowers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Echeveria 'Devotion'</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Echeveria pulvinata 'Bcec12001' (Devotion)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Full sun or very bright light.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Low; soak only after the root zone dries.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Tender H2: lift before frost and overwinter bright, frost-free and almost dry.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Velvety green leaves develop burgundy margins and tips in strong light and cool weather.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Sedum 'Atlantis'</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Sedum takesimense 'Nonsitnal' (Atlantis)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Low once established.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Cut back old flower stems in spring and divide if the mound opens in the centre.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Green leaves with broad cream-yellow margins blush pink in autumn; yellow summer flowers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Purple Fountain Grass 'Rubrum'</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Pennisetum advena 'Rubrum'</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Full sun in a warm, sheltered position.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Moderate during active growth; never leave waterlogged.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Tender H3: lift or pot before hard frost and overwinter frost-free; fleece alone is unreliable in Bromsgrove.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Arching burgundy leaves and purple-brown bottlebrush plumes from summer into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Ajuga 'Midnight Mystery'</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Ajuga reptans 'Midnight Mystery'</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade or gentle sun.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Moderate; keep moist while establishing.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Remove unwanted runners and maintain airflow to reduce mildew.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Dark bronze evergreen foliage with contrasting rosy-pink spring flowers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand Flax (dark)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Phormium 'Platt's Black'</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Moderate; drought-tolerant once established.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Remove old leaves at base. Architectural and low-care.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen dark foliage year-round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Stone Bed</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Agapanthus</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Agapanthus (species and cultivar unknown)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for reliable flowering.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Low once established; water during establishment and prolonged late-summer drought.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Grow in moisture-retentive but well-drained soil. Deadhead or retain seedheads deliberately and protect the crown in severe winter weather until hardiness is known.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Strap-shaped foliage photographed in August; flower colour and exact form remain unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Patio</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Honeysuckle</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Lonicera</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Sun, with shaded roots.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Moderate.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Light prune after flowering. Train onto support.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Fragrant flowers June–August.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Patio</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Clematis</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Clematis montana</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Sun, with shaded roots.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Moderate.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Group 1 clematis — light prune after flowering only. Tie in new growth.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Sheets of pale pink flowers May; vigorous summer growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Pear Tree</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Pyrus</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Full sun.</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Prefers well-drained, loamy soil. Requires regular watering during the establishment phase and prolonged dry periods, particularly when fruiting.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Requires annual winter pruning to maintain shape, remove dead wood, and encourage productive fruiting spurs. Monitor for common pests like aphids and diseases such as pear rust.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Deciduous. Blossoms in early spring, followed by leaf emergence and fruit development through summer. Harvest typically occurs in late summer or autumn, preceding leaf fall.</t>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Deep watering in dry summers.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Winter prune for shape. Thin fruit if heavy.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>White blossom April; fruit September; bare winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 1</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Fuchsia</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Fuchsia 'Mrs Popple'</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade to full sun.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Keep compost moist. Water daily in hot weather.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Red and purple pendant flowers June–October; deciduous in winter; new growth from the base in spring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 1</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Verbena</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Verbena 'Showboat Light Pink'</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Regular; don't let compost dry out.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead to keep flowering. Tender annual — replace yearly.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Clusters of soft pink flowers June–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 1</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Calibrachoa</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Calibrachoa 'Cabaret Special Pink Star'</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist. Hates drying out.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Feed weekly with liquid tomato food. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Pink star-patterned flowers May–October. Continuous if fed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 1</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Nepeta</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Nepeta (catmint)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Low to moderate. Drought-tolerant once established.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Cut back after first flush for a repeat. Aromatic — cats love it.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 1</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Lobelia</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade to full sun.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Keep moist at all times. Hates drying out.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Trim back leggy growth mid-season. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Deep blue and white trailing flowers May–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 1</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Petunia</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Petunia 'Midnight Sky'</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Regular; don't let compost dry out completely.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Dark purple-white trumpet flowers May–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 2</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Lobelia</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade to full sun.</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Keep moist at all times. Hates drying out.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Trim back leggy growth mid-season. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Deep blue and white trailing flowers May–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 2</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Verbena</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Verbena 'Venturi Pink Bicolour'</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Regular; don't let compost dry out.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead to keep flowering. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Pink bicolour flower clusters June–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 2</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Petunia</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Petunia 'Sky Purple White Sky'</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Regular; don't let compost dry out completely.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Purple-white striped trumpet flowers May–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 2</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Nepeta</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Nepeta (catmint)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Low to moderate. Drought-tolerant once established.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Cut back after first flush for a repeat. Aromatic.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Big Pot 2</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Fuchsia</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Fuchsia 'Mrs Popple'</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade to full sun.</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Keep compost moist. Water daily in hot weather.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Red and purple pendant flowers June–October; deciduous in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Little Pot 1</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Geranium</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Pelargonium 'Trend Sophie Dark Red'</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let compost dry slightly between waterings.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead regularly. Feed fortnightly. Not frost-hardy — overwinter indoors or treat as annual.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Dark red flower heads May–October; scented rounded leaves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Little Pot 1</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Petunia</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Petunia 'Vivini Blue Star'</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Regular; don't let compost dry out completely.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Blue-white star-patterned flowers May–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Little Pot 2</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Coreopsis Gold</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Coreopsis 'Gold'</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Moderate; the small pot dries quickly, but avoid permanently wet compost.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead regularly for continuous flowering. Cut tired growth back by up to half for a second flush and keep the pot freely drained through winter.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Bright golden-yellow daisy flowers June–September above a compact leafy mound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Cercis Pot</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Cercis 'Carolina Sweetheart'</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Cercis canadensis 'Nccc1'</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Full sun in a warm position; shelter the pot from severe drying wind.</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing. Water deeply when the upper compost starts to dry, without leaving the pot waterlogged.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Avoid routine pruning; remove only dead, damaged or crossing growth. Refresh the compost surface in spring and plan for a larger root run as the tree matures.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Heart-shaped leaves open maroon-red and mature through green, cream and pink variegation; bare branches may carry pink-purple flowers in spring as the tree matures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Front Pot</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Gazania 'Sunny Side Up'</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Gazania rigens 'Sunny Side Up'</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Full sun. Flowers close in shade and on overcast days.</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Low to moderate. Drought-tolerant. Sharp drainage.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead spent flowers to encourage more. Tender annual — replace each year. Does not recover from frost.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Large cream-white daisy flowers with contrasting dark centres May–October; closes at night and on dull days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Front Pot</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Gazania 'Orange Flame'</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Gazania rigens 'Orange Flame'</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Full sun. Flowers close in shade.</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Low to moderate. Drought-tolerant.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead to extend flowering. Tender annual — replace each year. Not frost-hardy.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Vivid orange flame-patterned daisy flowers May–October; closes at night and on dull days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Front Pot</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Calibrachoa</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Calibrachoa spp.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist. Hates drying out.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Feed weekly with liquid tomato food. Self-cleaning — no deadheading needed. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Masses of small petunia-like flowers May–October. Continuous if fed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Front Pot</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Bacopa White</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Sutera cordata (white cultivar)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade.</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Tiny white flowers May–October; neat trailing habit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Wall Pot 1</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Candy House Mix</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Calibrachoa 'Candy House Mix'</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Regular; do not let dry out. Water at the base.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Feed weekly with liquid tomato food. Deadhead spent flowers. Tender annual — replace each season. Trim back if leggy to encourage bushy growth.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Prolific trailing flowers in mixed red, yellow and pink June–October; dies with first frost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Wall Pot 2</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Echinacea 'Mooodz Glory'</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Echinacea 'Hilmooglor'</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for strongest flowering; tolerates partial shade.</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Water thoroughly, then let the upper compost begin to dry; never leave the crown in cold, wet compost.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead fading flowers for further blooms, or retain selected cones for winter structure. Protect the pot from prolonged winter saturation.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>White, slightly drooping petals around golden-green cones from summer into autumn; dies back to a hardy crown in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Baskets</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Trailing Fuchsia</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Fuchsia (trailing cultivar)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade to full sun.</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Daily in hot weather; never let dry out completely.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Feed weekly. Deadhead spent flowers. Not frost-hardy — replace each year.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Pendant bicolour flowers June–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Baskets</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Bacopa</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Sutera cordata</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Tiny white flowers May–October; neat trailing habit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Baskets</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Trailing Lobelia</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Lobelia erinus (trailing)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade.</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Keep moist; hates drying out.</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Trim back mid-season if it gets straggly. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Blue trailing flowers May–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Baskets</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Trailing Verbena</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Verbena (trailing cultivar)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Regular; don't let dry out.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead to extend flowering. Tender annual.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Clusters of flowers June–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Baskets</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Petunia</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Petunia (cultivar unknown)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade.</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Check daily in warm weather; water thoroughly before the basket dries out.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Feed weekly during flowering and remove faded blooms and seed capsules. Trim bare stems back to leafy growth.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Funnel-shaped summer flowers from June until the first frost; cultivar unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 1</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Hydrangea</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Hydrangea macrophylla</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Morning sun, afternoon shade.</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Thirsty — water well in dry spells.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Mophead flowers July–Sept; bare in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 1</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Lavandula angustifolia</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Drought-tolerant.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Purple spikes June–Aug; aromatic year-round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 2</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Coprosma 'Inferno'</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Coprosma 'Inferno'</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Moderate while establishing. Avoid waterlogged soil.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 2</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Coprosma 'Pina Colada'</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Coprosma 'Pina Colada'</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Moderate while establishing. Let the soil drain between waterings.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 2</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Coprosma 'City Knights'</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Coprosma 'City Knights'</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 2</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Hebe 'Kiwi' (Horopito)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Hebe 'Kiwi'</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade in a sheltered position.</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 2</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Polemonium 'Golden Feathers'</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Polemonium 'Golden Feathers'</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 3</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Climbing Rose 'Super Fairy'</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Rosa 'Helsufair'</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Sun to light partial shade.</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Deep water at the base in dry spells, especially while establishing.</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 3</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Variegated Dogwood</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Cornus alba 'Elegantissima'</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 3</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Red Hot Poker</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Kniphofia</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for the strongest flowering.</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 3</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Leucothoe 'Little Flames'</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Leucothoe 'Little Flames'</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 3</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Rose (pink)</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Rosa — IDENTIFY</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Sun.</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Deep watering, mulch in spring.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Prune late winter; deadhead through summer.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Flowers June–Sept; bare winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Photinia (existing canopy)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Photinia (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade.</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Water deeply only in prolonged dry periods once established.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>The Pilgrim</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Rosa 'Auswalker'</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Deep water at the base during dry spells, especially while establishing.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>The Generous Gardener</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Rosa 'Ausdrawn'</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Deep water at the base during dry spells, especially in its first two years.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Physocarpus Cluster 1 (2 × Little Devil)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Physocarpus opulifolius 'Little Devil'</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade; foliage is darkest with good light.</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Water both root balls deeply in dry spells for the first two growing seasons; then only during prolonged drought.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Treat as two compact deciduous ninebarks. Keep each crown distinct and remove a few oldest stems at ground level only once established; avoid clipping the cluster into one solid ball.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Burgundy-purple foliage spring to autumn; pale pinkish-white flowers in early summer; bare in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Physocarpus Cluster 2 (2 × Lady in Red)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Physocarpus opulifolius 'Lady in Red'</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade; best foliage colour in brighter light.</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Water both root balls deeply in dry spells while establishing; afterwards they are fairly drought tolerant.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Treat as two deciduous ninebarks. Keep their layered outlines distinct and remove a few oldest stems at the base in late winter only when congestion develops.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Fresh red foliage matures bronze-purple; pink flower clusters in summer; bare in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Physocarpus Cluster 3 (2 × Little Devil + 1 × Lady in Red)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade; brighter light strengthens the burgundy and red-bronze foliage.</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Water all three root balls deeply in dry spells while establishing; afterwards the cluster is fairly drought tolerant.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Keep the two lower Little Devils and taller Lady in Red readable as a layered trio. Renew individual shrubs from the base only when mature and congested; do not shear the cluster into one mass.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Magic Carpet</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Spiraea japonica 'Magic Carpet'</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Sun to light partial shade; brighter light gives the strongest gold foliage.</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Water regularly during its first summer, then only in prolonged dry spells.</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Lightly trim after flowering or cut back by about a third in early spring to encourage colourful new growth.</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Gold foliage with red young growth, deep-pink summer flowers and warm autumn colour; deciduous in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Purple Gem</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Shade to partial shade.</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Rhododendron 'Libretto'</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Rhododendron 'Libretto'</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Festuca 'Elijah Blue' (3 plants)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Festuca glauca 'Elijah Blue'</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade.</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Water regularly during the first season; drought tolerant once established.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Pieris 'Polar Passion'</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Dahlia 'Tampico'</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Full sun, sheltered from strong wind.</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Verbena 'Margaret's Memory'</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Glandularia 'Margaret's Memory'</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade.</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Delosperma 'Ice Cream Mix'</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Delosperma cooperi Ice Cream Series</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Full sun; flowers open best in bright, warm conditions.</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Drought-tolerant once established. Water sparingly and never leave the crown in wet winter soil.</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Sharp drainage is essential. Avoid rich feeding, trim away damaged growth in spring and protect from prolonged severe frost if the soil is wet.</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>A low evergreen succulent mat with mixed pink, orange and yellow daisy flowers from summer into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 4</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Achillea</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Achillea millefolium</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Low to moderate. Drought-tolerant once established.</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Mexican Orange Blossom</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Choisya ternata 'Sundance'</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Sun for best colour.</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Moderate.</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Light prune after flowering to shape. Low-care.</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Shrub Rose (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Rosa (Shrub Group; cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Bay Tree</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Laurus nobilis</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade in a sheltered position.</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Japanese Skimmia</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia japonica (cultivar and sex to confirm)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Hardy Fuchsia (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Clematis (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Clematis viticella (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade, with a cool shaded root run.</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Deciduous climber with abundant summer flowers on new growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Hydrangea 'Bloody Marie'</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Hydrangea paniculata 'Bloody Marie'</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Euphorbia 'Ascot Petite'</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Euphorbia × martinii 'Ascot Petite'</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Full sun in a sheltered position.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Flaming Silver</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Pieris japonica 'Flaming Silver'</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Astrantia trio</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Sun to light shade.</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Pittosporum 'Tom Thumb'</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade in a sheltered position.</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Gaura 'Gaudi Red'</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Full sun in a warm, sheltered position.</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Heather 'Bell's Extra Special'</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Erica carnea 'Bell's Extra Special'</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Heather 'Tib'</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Calluna vulgaris 'Tib'</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for compact growth and the best flower display.</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Bell Heather 'Providence' (2 plants)</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Daboecia cantabrica 'Providence'</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Heather 'Leprechaun'</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Calluna vulgaris 'Leprechaun'</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for the brightest foliage colour.</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Heather 'Winter Chocolate'</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Calluna vulgaris 'Winter Chocolate'</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Ceratostigma</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Ceratostigma plumbaginoides</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Hypericum (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Hypericum (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Bluebell Creeper</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade in a warm, sheltered position.</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Hebe 'Rhubarb and Custard'</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to partial shade in a warm, sheltered spot.</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Salvia 'Salgoon Lake Blueberry'</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Full sun in a warm, sheltered position.</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Front Bed 5</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Little Devil</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Physocarpus opulifolius 'Little Devil'</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade; foliage is darkest with good light.</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Water deeply in dry spells for the first two growing seasons; then only during prolonged drought.</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Compact deciduous ninebark. Remove a few of the oldest stems at ground level in late winter once established; avoid clipping into a tight ball.</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Burgundy-purple foliage spring to autumn; pale pinkish-white flowers in early summer; bare in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Front Stone Trough</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Hosta</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Hosta</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Part to full shade.</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Keep moist; never bone-dry in the trough.</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Watch for slugs/snails. Divide clumps in spring.</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Fresh leaves spring; dies back over winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Front Box Hedge</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Wall Cotoneaster (species to confirm)</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Cotoneaster (species to confirm)</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Sun to part shade.</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Front Pots</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Mixed Pot</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Mixed seasonal planting — contents to confirm</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Front Pots</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Fuchsia Pot</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Fuchsia cultivars — identities to confirm</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Front Fruit Trees</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Apple Tree</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Malus domestica</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Full sun.</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Water well in dry spells while fruiting.</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Blossom April–May; fruit late summer–autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Front Fruit Trees</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Damson Tree</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for reliable blossom and fruit ripening.</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Front Gate Tree</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Weeping Crab Apple (cultivar to confirm)</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>House · Hallway · Kentia Palm</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Kentia Palm — assumed</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Howea forsteriana</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Nemesia Pot</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Nemesia 'Lady Penelope'</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Full sun to light partial shade in a sheltered position.</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Keep the container evenly moist but never waterlogged.</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum Pot</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus Spirit</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus 'Anvi' (Spirit)</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Sun or partial shade, with shelter from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Pink buds open to lightly fragrant creamy-white flowers from late winter into spring, followed by blue-black ornamental berries.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:G159"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -4971,32 +4971,32 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Delosperma 'Ice Cream Mix'</t>
+          <t>Calluna Trio Mix (3 plants)</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Delosperma cooperi Ice Cream Series</t>
+          <t>Calluna vulgaris mixed cultivars</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Full sun; flowers open best in bright, warm conditions.</t>
+          <t>Full sun in an open position.</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Drought-tolerant once established. Water sparingly and never leave the crown in wet winter soil.</t>
+          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Sharp drainage is essential. Avoid rich feeding, trim away damaged growth in spring and protect from prolonged severe frost if the soil is wet.</t>
+          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>A low evergreen succulent mat with mixed pink, orange and yellow daisy flowers from summer into autumn.</t>
+          <t>A three-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
         </is>
       </c>
     </row>

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$162</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1382,32 +1382,32 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Sedum 'Rose Carpet'</t>
+          <t>Magic Carpet</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Sedum pluricaule 'Rose Carpet'</t>
+          <t>Spiraea japonica 'Walbuma' (Magic Carpet)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade.</t>
+          <t>Full sun to light partial shade; brighter light gives the strongest gold foliage.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Low once established; allow the soil surface to dry and avoid winter saturation.</t>
+          <t>Sprinkler supplied. Keep evenly moist while re-establishing, then water during prolonged dry spells.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Keep in sharply drained neutral to alkaline soil. Cut back after flowering and divide in spring if needed.</t>
+          <t>Lightly trim after flowering or renovate immediately after flowering if it becomes overgrown. Keep its lower golden outline distinct from the four Double Play Big Bang shrubs.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Grey-green succulent leaves and dense rose-pink flower clusters in late summer; dormant in winter.</t>
+          <t>Red new leaves mature gold, with deep-pink summer flowers and warm autumn colour; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -1419,32 +1419,32 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Weeping Cherry</t>
+          <t>Sedum 'Rose Carpet'</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Prunus species</t>
+          <t>Sedum pluricaule 'Rose Carpet'</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Moderate; deep watering when young.</t>
+          <t>Low once established; allow the soil surface to dry and avoid winter saturation.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Light pruning after flowering; avoid heavy cuts.</t>
+          <t>Keep in sharply drained neutral to alkaline soil. Cut back after flowering and divide in spring if needed.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Pink blossom April; green canopy summer; bare winter.</t>
+          <t>Grey-green succulent leaves and dense rose-pink flower clusters in late summer; dormant in winter.</t>
         </is>
       </c>
     </row>
@@ -1456,32 +1456,32 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Rose (inherited)</t>
+          <t>Weeping Cherry</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Rosa (cultivar unknown)</t>
+          <t>Prunus species</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Best in full sun; tolerates light partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during sustained dry spells, checking the soil first.</t>
+          <t>Moderate; deep watering when young.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Mulch and feed in spring. Deadhead if it repeats and delay class-specific pruning until its growth habit is documented.</t>
+          <t>Light pruning after flowering; avoid heavy cuts.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Yellow summer flowers and developing buds photographed in August; repeat pattern and hip production still to be recorded.</t>
+          <t>Pink blossom April; green canopy summer; bare winter.</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Evergreen Candytuft — assumed</t>
+          <t>Rose (inherited)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Iberis sempervirens (assumed)</t>
+          <t>Rosa (cultivar unknown)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Full sun for compact growth and reliable flowering.</t>
+          <t>Best in full sun; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Low once established; avoid stagnant winter moisture.</t>
+          <t>Water deeply during sustained dry spells, checking the soil first.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Grow in sharply drained soil. Trim lightly after flowering to keep the evergreen mound compact; retain the assumed qualification until flowers or a label confirm it.</t>
+          <t>Mulch and feed in spring. Deadhead if it repeats and delay class-specific pruning until its growth habit is documented.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Evergreen narrow foliage with white spring flowers expected if the provisional identification is correct.</t>
+          <t>Yellow summer flowers and developing buds photographed in August; repeat pattern and hip production still to be recorded.</t>
         </is>
       </c>
     </row>
@@ -1530,69 +1530,69 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Variegated Lesser Periwinkle — assumed</t>
+          <t>Evergreen Candytuft — assumed</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor (variegated cultivar; assumed)</t>
+          <t>Iberis sempervirens (assumed)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to shade; tolerates sun where soil stays moist.</t>
+          <t>Full sun for compact growth and reliable flowering.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate once established; water in prolonged drought.</t>
+          <t>Low once established; avoid stagnant winter moisture.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Trim spreading stems where they cross paths or smother neighbours. Keep the cultivar unresolved until flowers, leaf detail or a label provide stronger evidence.</t>
+          <t>Grow in sharply drained soil. Trim lightly after flowering to keep the evergreen mound compact; retain the assumed qualification until flowers or a label confirm it.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Evergreen cream-edged foliage; violet-blue spring flowers expected if the provisional identification is correct.</t>
+          <t>Evergreen narrow foliage with white spring flowers expected if the provisional identification is correct.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Bed 4</t>
+          <t>Bed 3</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Apple Tree</t>
+          <t>Variegated Lesser Periwinkle — assumed</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Malus domestica</t>
+          <t>Vinca minor (variegated cultivar; assumed)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to shade; tolerates sun where soil stays moist.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Deep watering in dry spells, especially when fruiting.</t>
+          <t>Low to moderate once established; water in prolonged drought.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Winter prune for shape. Thin fruit in June for size.</t>
+          <t>Trim spreading stems where they cross paths or smother neighbours. Keep the cultivar unresolved until flowers, leaf detail or a label provide stronger evidence.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Blossom April; fruit August–October; bare winter.</t>
+          <t>Evergreen cream-edged foliage; violet-blue spring flowers expected if the provisional identification is correct.</t>
         </is>
       </c>
     </row>
@@ -1604,32 +1604,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Callistemon Inferno ('Yanferno')</t>
+          <t>Apple Tree</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Callistemon Inferno ('Yanferno')</t>
+          <t>Malus domestica</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Full sun. Thrives in a warm, sheltered spot.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Drought-tolerant once established. Good drainage essential.</t>
+          <t>Deep watering in dry spells, especially when fruiting.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>RHS hardiness H3 (about −5°C to 1°C). Keep in a warm, sheltered position and protect thoroughly from severe cold and winter winds. Prune only in summer immediately after flowering, removing a little older growth at a time.</t>
+          <t>Winter prune for shape. Thin fruit in June for size.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Evergreen; vivid red bottlebrush flowers June–August, sometimes a repeat flush in autumn. Architectural foliage year-round.</t>
+          <t>Blossom April; fruit August–October; bare winter.</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Gaillardia</t>
+          <t>Callistemon Inferno ('Yanferno')</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Gaillardia × grandiflora</t>
+          <t>Callistemon Inferno ('Yanferno')</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun. Thrives in a warm, sheltered spot.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Sharp drainage essential — hates wet feet.</t>
+          <t>Moderate. Drought-tolerant once established. Good drainage essential.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Deadhead regularly for near-continuous bloom. Cut back hard in autumn. Short-lived perennial — may need replacing every 2–3 years.</t>
+          <t>RHS hardiness H3 (about −5°C to 1°C). Keep in a warm, sheltered position and protect thoroughly from severe cold and winter winds. Prune only in summer immediately after flowering, removing a little older growth at a time.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Vivid red, orange and yellow daisy-like flowers June–October; near-continuous if deadheaded.</t>
+          <t>Evergreen; vivid red bottlebrush flowers June–August, sometimes a repeat flush in autumn. Architectural foliage year-round.</t>
         </is>
       </c>
     </row>
@@ -1678,32 +1678,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Abelia 'Kaleidoscope'</t>
+          <t>Gaillardia</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Abelia × grandiflora 'Kaleidoscope'</t>
+          <t>Gaillardia × grandiflora</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade. Best foliage colour in full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Good drainage.</t>
+          <t>Low to moderate. Sharp drainage essential — hates wet feet.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Light trim after flowering to maintain shape. Very low maintenance. Semi-evergreen — may drop some leaves in a hard winter but recovers readily.</t>
+          <t>Deadhead regularly for near-continuous bloom. Cut back hard in autumn. Short-lived perennial — may need replacing every 2–3 years.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Variegated yellow and green leaves spring–summer, turning orange-red in autumn; small white fragrant flowers July–September. Semi-evergreen.</t>
+          <t>Vivid red, orange and yellow daisy-like flowers June–October; near-continuous if deadheaded.</t>
         </is>
       </c>
     </row>
@@ -1715,69 +1715,69 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Lobelia 'Starship Scarlet Bronze Leaf'</t>
+          <t>Abelia 'Kaleidoscope'</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Lobelia × speciosa 'Starship Scarlet Bronze Leaf'</t>
+          <t>Abelia × grandiflora 'Kaleidoscope'</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade. Best flowering with at least half a day of sun.</t>
+          <t>Full sun to partial shade. Best foliage colour in full sun.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist; do not allow the compost to dry out in summer.</t>
+          <t>Moderate. Good drainage.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while it establishes. Deadhead spent spikes; mulch the crown for winter and avoid stagnant soil.</t>
+          <t>Light trim after flowering to maintain shape. Very low maintenance. Semi-evergreen — may drop some leaves in a hard winter but recovers readily.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Bronze foliage from spring; tall scarlet flower spikes July–September; dies back in winter and returns from the crown.</t>
+          <t>Variegated yellow and green leaves spring–summer, turning orange-red in autumn; small white fragrant flowers July–September. Semi-evergreen.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Bed 5</t>
+          <t>Bed 4</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Wisteria</t>
+          <t>Lobelia 'Starship Scarlet Bronze Leaf'</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Wisteria spp.</t>
+          <t>Lobelia × speciosa 'Starship Scarlet Bronze Leaf'</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade. Best flowering with at least half a day of sun.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Deep watering when young; established plants tolerate drought.</t>
+          <t>Keep evenly moist; do not allow the compost to dry out in summer.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Prune twice yearly: August (long shoots to 6 leaves) and February (back to 2–3 buds).</t>
+          <t>Keep evenly moist while it establishes. Deadhead spent spikes; mulch the crown for winter and avoid stagnant soil.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Lilac racemes May; bare gnarled stems winter.</t>
+          <t>Bronze foliage from spring; tall scarlet flower spikes July–September; dies back in winter and returns from the crown.</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Wisteria</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>Wisteria spp.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1804,17 +1804,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Deep watering, mulch in spring.</t>
+          <t>Deep watering when young; established plants tolerate drought.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Prune in late winter. Feed in spring and after first flush.</t>
+          <t>Prune twice yearly: August (long shoots to 6 leaves) and February (back to 2–3 buds).</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Flowers June–September; bare winter.</t>
+          <t>Lilac racemes May; bare gnarled stems winter.</t>
         </is>
       </c>
     </row>
@@ -1826,32 +1826,32 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>New Zealand Flax (cultivar to confirm)</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Phormium (cultivar to confirm)</t>
+          <t>Rosa</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; shelter from cold drying winds.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; drought-tolerant later, but avoid prolonged waterlogging.</t>
+          <t>Deep watering, mulch in spring.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Grow in fertile, well-drained soil. Remove damaged leaves at the base in spring and mulch the crown before hard frost. Cultivar still needs confirmation from a label or diagnostic photos.</t>
+          <t>Prune in late winter. Feed in spring and after first flush.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Evergreen sword-shaped foliage year-round; mature plants may produce tall flower stems in summer.</t>
+          <t>Flowers June–September; bare winter.</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Alstroemeria</t>
+          <t>New Zealand Flax (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Alstroemeria hybrid</t>
+          <t>Phormium (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; flowering is strongest with plenty of light.</t>
+          <t>Full sun to partial shade; shelter from cold drying winds.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist in the growing season, but never waterlogged.</t>
+          <t>Moderate while establishing; drought-tolerant later, but avoid prolonged waterlogging.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly while flowering. Pull spent flower stems cleanly from the base rather than cutting them. Protect the pot from hard frost in winter.</t>
+          <t>Grow in fertile, well-drained soil. Remove damaged leaves at the base in spring and mulch the crown before hard frost. Cultivar still needs confirmation from a label or diagnostic photos.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Red-and-gold flowers from summer into autumn above dark foliage; dies back in cold weather.</t>
+          <t>Evergreen sword-shaped foliage year-round; mature plants may produce tall flower stems in summer.</t>
         </is>
       </c>
     </row>
@@ -1900,32 +1900,32 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Bee's Knees'</t>
+          <t>Alstroemeria</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Bee's Knees'</t>
+          <t>Alstroemeria hybrid</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the most flowers; tolerates light partial shade.</t>
+          <t>Full sun to partial shade; flowering is strongest with plenty of light.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Water when the top of the compost begins to dry; pots may need daily checks in hot weather.</t>
+          <t>Keep evenly moist in the growing season, but never waterlogged.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with a high-potash liquid feed and deadhead or trim leggy growth to keep flowers coming.</t>
+          <t>Feed weekly while flowering. Pull spent flower stems cleanly from the base rather than cutting them. Protect the pot from hard frost in winter.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Clear yellow flowers from summer until the first frost; grown as a tender annual.</t>
+          <t>Red-and-gold flowers from summer into autumn above dark foliage; dies back in cold weather.</t>
         </is>
       </c>
     </row>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Petunia 'Bee's Knees'</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Petunia 'Bee's Knees'</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Sun to shade; the yellow-and-green foliage colours best in bright indirect light or partial shade.</t>
+          <t>Full sun for the most flowers; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface dry slightly between waterings, without letting the pot dry out completely.</t>
+          <t>Water when the top of the compost begins to dry; pots may need daily checks in hot weather.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Trim trailing stems to shape. Hardy and evergreen, but vigorous if later planted into open ground.</t>
+          <t>Feed weekly with a high-potash liquid feed and deadhead or trim leggy growth to keep flowers coming.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Golden variegated foliage year-round with small violet-blue flowers mainly in spring.</t>
+          <t>Clear yellow flowers from summer until the first frost; grown as a tender annual.</t>
         </is>
       </c>
     </row>
@@ -1974,32 +1974,32 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Nemesia</t>
+          <t>Vinca minor 'Illumination'</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nemesia hybrid</t>
+          <t>Vinca minor 'Illumination'</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; a little afternoon shade helps during hot spells.</t>
+          <t>Sun to shade; the yellow-and-green foliage colours best in bright indirect light or partial shade.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Keep the compost evenly moist but not waterlogged; check the pot frequently in warm or windy weather.</t>
+          <t>Moderate. Let the surface dry slightly between waterings, without letting the pot dry out completely.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Feed fortnightly while flowering. Deadhead or trim back tired stems by about a third to encourage a fresh flush.</t>
+          <t>Trim trailing stems to shape. Hardy and evergreen, but vigorous if later planted into open ground.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Small, scented flowers from summer into autumn; usually grown as tender seasonal colour.</t>
+          <t>Golden variegated foliage year-round with small violet-blue flowers mainly in spring.</t>
         </is>
       </c>
     </row>
@@ -2011,32 +2011,32 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Lythrum 'Robin'</t>
+          <t>Nemesia</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Lythrum salicaria 'Robin'</t>
+          <t>Nemesia hybrid</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; flowers best in full sun.</t>
+          <t>Full sun to light partial shade; a little afternoon shade helps during hot spells.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Moisture-loving. Keep the compost consistently moist, especially during flowering.</t>
+          <t>Keep the compost evenly moist but not waterlogged; check the pot frequently in warm or windy weather.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to prolong flowering or leave some seedheads for wildlife. Cut old stems down in late winter or early spring.</t>
+          <t>Feed fortnightly while flowering. Deadhead or trim back tired stems by about a third to encourage a fresh flush.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Dense magenta flower spikes in summer, popular with bees; herbaceous and dormant in winter.</t>
+          <t>Small, scented flowers from summer into autumn; usually grown as tender seasonal colour.</t>
         </is>
       </c>
     </row>
@@ -2048,32 +2048,32 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Begonia 'Carmen'</t>
+          <t>Lythrum 'Robin'</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Begonia 'Carmen'</t>
+          <t>Lythrum salicaria 'Robin'</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Bright partial shade or gentle morning sun; protect from harsh midday sun.</t>
+          <t>Full sun to partial shade; flowers best in full sun.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but not saturated. Water the compost rather than the leaves and flowers.</t>
+          <t>Moisture-loving. Keep the compost consistently moist, especially during flowering.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded blooms and feed fortnightly in summer. Tender — protect from frost and overwinter under cover if keeping it.</t>
+          <t>Deadhead to prolong flowering or leave some seedheads for wildlife. Cut old stems down in late winter or early spring.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Double red flowers through summer and early autumn; tender and dormant or discarded after frost.</t>
+          <t>Dense magenta flower spikes in summer, popular with bees; herbaceous and dormant in winter.</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Aroma Heart of Gold'</t>
+          <t>Begonia 'Carmen'</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nemesia Aroma Heart of Gold (Aroma Series)</t>
+          <t>Begonia 'Carmen'</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Bright partial shade or gentle morning sun; protect from harsh midday sun.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained, watering in dry spells to maintain flowering.</t>
+          <t>Keep evenly moist but not saturated. Water the compost rather than the leaves and flowers.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Pinch the growing tips for a bushy plant. Trim flowering shoots after the first flush to encourage more blooms; protect cuttings from frost if overwintering.</t>
+          <t>Deadhead faded blooms and feed fortnightly in summer. Tender — protect from frost and overwinter under cover if keeping it.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Sweetly fragrant burgundy-red and creamy-yellow flowers with burnt-orange centres from summer into autumn.</t>
+          <t>Double red flowers through summer and early autumn; tender and dormant or discarded after frost.</t>
         </is>
       </c>
     </row>
@@ -2122,49 +2122,49 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Cabbage Tree</t>
+          <t>Nemesia 'Aroma Heart of Gold'</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Cordyline australis 'Red Star'</t>
+          <t>Nemesia Aroma Heart of Gold (Aroma Series)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Moderate; established plants tolerate drought.</t>
+          <t>Keep moist but well drained, watering in dry spells to maintain flowering.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Tie up leaves in winter to protect crown if hard frost forecast.</t>
+          <t>Pinch the growing tips for a bushy plant. Trim flowering shoots after the first flush to encourage more blooms; protect cuttings from frost if overwintering.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Evergreen burgundy fountain of leaves.</t>
+          <t>Sweetly fragrant burgundy-red and creamy-yellow flowers with burnt-orange centres from summer into autumn.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Stone Bed</t>
+          <t>Bed 5</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Houseleeks</t>
+          <t>Cabbage Tree</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum</t>
+          <t>Cordyline australis 'Red Star'</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Very low. Hates wet.</t>
+          <t>Moderate; established plants tolerate drought.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Sharp drainage; almost no maintenance.</t>
+          <t>Tie up leaves in winter to protect crown if hard frost forecast.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Evergreen rosettes; flowering rosettes die after blooming, replaced by offsets.</t>
+          <t>Evergreen burgundy fountain of leaves.</t>
         </is>
       </c>
     </row>
@@ -2196,32 +2196,32 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Echeveria</t>
+          <t>Houseleeks</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Echeveria cultivar</t>
+          <t>Sempervivum</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Full sun or very bright light; acclimatise gradually to strong sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Low. Water only when the soil has dried; keep almost dry in winter.</t>
+          <t>Very low. Hates wet.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Sharply drained soil. Tender: lift before frost and overwinter frost-free under cover.</t>
+          <t>Sharp drainage; almost no maintenance.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Evergreen powdery grey-purple rosette; pink-red flower stems may appear in summer.</t>
+          <t>Evergreen rosettes; flowering rosettes die after blooming, replaced by offsets.</t>
         </is>
       </c>
     </row>
@@ -2233,32 +2233,32 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Sedum 'Chocolate Ball'</t>
+          <t>Echeveria</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Sedum polytrichoides 'Chocolate Ball'</t>
+          <t>Echeveria cultivar</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun or very bright light; acclimatise gradually to strong sun.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Very low; let the gritty soil dry between waterings.</t>
+          <t>Low. Water only when the soil has dried; keep almost dry in winter.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Sharp drainage is essential. RHS H3: protect from severe frost and prolonged winter wet.</t>
+          <t>Sharply drained soil. Tender: lift before frost and overwinter frost-free under cover.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Evergreen bronze-brown foliage; small yellow flowers in summer.</t>
+          <t>Evergreen powdery grey-purple rosette; pink-red flower stems may appear in summer.</t>
         </is>
       </c>
     </row>
@@ -2270,32 +2270,32 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Older Caucasian Stonecrop</t>
+          <t>Sedum 'Chocolate Ball'</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Phedimus spurius cultivar</t>
+          <t>Sedum polytrichoides 'Chocolate Ball'</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Full sun for compact growth and strongest colour.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Low; water only during establishment or prolonged drought.</t>
+          <t>Very low; let the gritty soil dry between waterings.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Trim spent flower stems and pull wandering shoots back from smaller alpines. Keep the crown sharply drained.</t>
+          <t>Sharp drainage is essential. RHS H3: protect from severe frost and prolonged winter wet.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Scalloped green leaves flush red; pink-red flower clusters age to brown seedheads.</t>
+          <t>Evergreen bronze-brown foliage; small yellow flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2307,32 +2307,32 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Common Houseleek</t>
+          <t>Older Caucasian Stonecrop</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum tectorum</t>
+          <t>Phedimus spurius cultivar</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun for compact growth and strongest colour.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Very low; established rosettes normally need no extra water.</t>
+          <t>Low; water only during establishment or prolonged drought.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Keep grit around the crowns, clear trapped leaves and remove a parent rosette only after it flowers and dies naturally.</t>
+          <t>Trim spent flower stems and pull wandering shoots back from smaller alpines. Keep the crown sharply drained.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Evergreen rosettes colour more strongly in cold or bright conditions; starry flowers may appear in summer.</t>
+          <t>Scalloped green leaves flush red; pink-red flower clusters age to brown seedheads.</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Six-rowed Stonecrop</t>
+          <t>Common Houseleek</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Sedum sexangulare</t>
+          <t>Sempervivum tectorum</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Very low once rooted.</t>
+          <t>Very low; established rosettes normally need no extra water.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Use gritty, lean soil and trim spreading stems where they crowd slower alpines.</t>
+          <t>Keep grit around the crowns, clear trapped leaves and remove a parent rosette only after it flowers and dies naturally.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Evergreen cylindrical leaves in six neat ranks; yellow star flowers in summer.</t>
+          <t>Evergreen rosettes colour more strongly in cold or bright conditions; starry flowers may appear in summer.</t>
         </is>
       </c>
     </row>
@@ -2381,32 +2381,32 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Ajuga 'Fancy Finch'</t>
+          <t>Six-rowed Stonecrop</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Ajuga 'Fanfin' (Feathered Friends Fancy Finch)</t>
+          <t>Sedum sexangulare</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Partial shade; protect the golden foliage from scorching midday sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Keep evenly moist while establishing.</t>
+          <t>Very low once rooted.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Trim spent flower spikes and remove runners that stray into the driest succulent pockets.</t>
+          <t>Use gritty, lean soil and trim spreading stems where they crowd slower alpines.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Golden to orange narrow foliage year-round; blue flower spikes in spring.</t>
+          <t>Evergreen cylindrical leaves in six neat ranks; yellow star flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2418,32 +2418,32 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea 'Snowflake'</t>
+          <t>Ajuga 'Fancy Finch'</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea quercifolia 'Brido' (Snowflake)</t>
+          <t>Ajuga 'Fanfin' (Feathered Friends Fancy Finch)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; afternoon shade is useful in hot weather.</t>
+          <t>Partial shade; protect the golden foliage from scorching midday sun.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Moderate to high while establishing; soak deeply during dry spells.</t>
+          <t>Moderate. Keep evenly moist while establishing.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Give it a humus-rich pocket beneath the gravel, mulch clear of the crown and prune only dead or misplaced wood after flowering.</t>
+          <t>Trim spent flower spikes and remove runners that stray into the driest succulent pockets.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Double white flower panicles fade pink; oak-shaped leaves turn rich red and purple in autumn.</t>
+          <t>Golden to orange narrow foliage year-round; blue flower spikes in spring.</t>
         </is>
       </c>
     </row>
@@ -2455,32 +2455,32 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Chick Charms Houseleek Mix</t>
+          <t>Hydrangea 'Snowflake'</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum Chick Charms Series</t>
+          <t>Hydrangea quercifolia 'Brido' (Snowflake)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to partial shade; afternoon shade is useful in hot weather.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Very low; only newly planted offsets need occasional water.</t>
+          <t>Moderate to high while establishing; soak deeply during dry spells.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>The label confirms the series but not its individual cultivars. Keep crowns dry and remove spent flowering rosettes.</t>
+          <t>Give it a humus-rich pocket beneath the gravel, mulch clear of the crown and prune only dead or misplaced wood after flowering.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Evergreen rosettes change colour with season and temperature; mature rosettes may flower in summer.</t>
+          <t>Double white flower panicles fade pink; oak-shaped leaves turn rich red and purple in autumn.</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Achillea 'King Alfred'</t>
+          <t>Chick Charms Houseleek Mix</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Achillea 'King Alfred'</t>
+          <t>Sempervivum Chick Charms Series</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Low once established.</t>
+          <t>Very low; only newly planted offsets need occasional water.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Keep in lean, sharply drained soil and trim untidy growth in spring.</t>
+          <t>The label confirms the series but not its individual cultivars. Keep crowns dry and remove spent flowering rosettes.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Low grey-green aromatic mat with pale yellow flower heads in late spring and early summer.</t>
+          <t>Evergreen rosettes change colour with season and temperature; mature rosettes may flower in summer.</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Golden Stonecrop 'Aureum'</t>
+          <t>Achillea 'King Alfred'</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Sedum acre 'Aureum'</t>
+          <t>Achillea 'King Alfred'</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2544,17 +2544,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Very low.</t>
+          <t>Low once established.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Avoid rich soil and trim after flowering if it spreads over slower plants.</t>
+          <t>Keep in lean, sharply drained soil and trim untidy growth in spring.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Evergreen yellow-gold foliage with small yellow flowers in summer.</t>
+          <t>Low grey-green aromatic mat with pale yellow flower heads in late spring and early summer.</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Cobweb Houseleek</t>
+          <t>Golden Stonecrop 'Aureum'</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum arachnoideum</t>
+          <t>Sedum acre 'Aureum'</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Keep winter rain and leaf litter out of the rosettes; detach offsets to extend the colony.</t>
+          <t>Avoid rich soil and trim after flowering if it spreads over slower plants.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Evergreen cobwebbed rosettes, often red-flushed; pink star flowers in summer.</t>
+          <t>Evergreen yellow-gold foliage with small yellow flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Thrift 'Armada White'</t>
+          <t>Cobweb Houseleek</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Armeria maritima 'Armada White'</t>
+          <t>Sempervivum arachnoideum</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate while establishing; drought tolerant later.</t>
+          <t>Very low.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Deadhead the white globes and keep the crown clear in gritty soil.</t>
+          <t>Keep winter rain and leaf litter out of the rosettes; detach offsets to extend the colony.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Evergreen grassy cushions with white flower heads from spring into summer.</t>
+          <t>Evergreen cobwebbed rosettes, often red-flushed; pink star flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Houseleek 'Purple Quartz'</t>
+          <t>Thrift 'Armada White'</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Sempervivum 'Purple Quartz' (Big Sam Series)</t>
+          <t>Armeria maritima 'Armada White'</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Very low.</t>
+          <t>Low to moderate while establishing; drought tolerant later.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Provide sharp drainage, clear debris and protect from persistent winter wet rather than cold.</t>
+          <t>Deadhead the white globes and keep the crown clear in gritty soil.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Grey-green rosettes flush pink and purple; mature rosettes flower once before offsets replace them.</t>
+          <t>Evergreen grassy cushions with white flower heads from spring into summer.</t>
         </is>
       </c>
     </row>
@@ -2677,32 +2677,32 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Sedum 'Angelina'</t>
+          <t>Houseleek 'Purple Quartz'</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Sedum rupestre 'Angelina'</t>
+          <t>Sempervivum 'Purple Quartz' (Big Sam Series)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Full sun for strongest gold and orange colour.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Very low once established.</t>
+          <t>Very low.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Shear or pull back spreading shoots when they overrun small rosettes.</t>
+          <t>Provide sharp drainage, clear debris and protect from persistent winter wet rather than cold.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Golden needle-like foliage turns orange in cold weather; yellow flowers in summer.</t>
+          <t>Grey-green rosettes flush pink and purple; mature rosettes flower once before offsets replace them.</t>
         </is>
       </c>
     </row>
@@ -2714,32 +2714,32 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Stonecrop 'Dragon's Blood'</t>
+          <t>Sedum 'Angelina'</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Phedimus spurius 'Schorbuser Blut'</t>
+          <t>Sedum rupestre 'Angelina'</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun for strongest gold and orange colour.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Low once established.</t>
+          <t>Very low once established.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Trim spent heads and keep spreading stems within their allotted gravel pocket.</t>
+          <t>Shear or pull back spreading shoots when they overrun small rosettes.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Green-red scalloped leaves deepen burgundy; clusters of deep pink-red summer flowers.</t>
+          <t>Golden needle-like foliage turns orange in cold weather; yellow flowers in summer.</t>
         </is>
       </c>
     </row>
@@ -2751,32 +2751,32 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Echeveria 'Devotion'</t>
+          <t>Stonecrop 'Dragon's Blood'</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Echeveria pulvinata 'Bcec12001' (Devotion)</t>
+          <t>Phedimus spurius 'Schorbuser Blut'</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Full sun or very bright light.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Low; soak only after the root zone dries.</t>
+          <t>Low once established.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Tender H2: lift before frost and overwinter bright, frost-free and almost dry.</t>
+          <t>Trim spent heads and keep spreading stems within their allotted gravel pocket.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Velvety green leaves develop burgundy margins and tips in strong light and cool weather.</t>
+          <t>Green-red scalloped leaves deepen burgundy; clusters of deep pink-red summer flowers.</t>
         </is>
       </c>
     </row>
@@ -2788,32 +2788,32 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Sedum 'Atlantis'</t>
+          <t>Echeveria 'Devotion'</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Sedum takesimense 'Nonsitnal' (Atlantis)</t>
+          <t>Echeveria pulvinata 'Bcec12001' (Devotion)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun or very bright light.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Low once established.</t>
+          <t>Low; soak only after the root zone dries.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Cut back old flower stems in spring and divide if the mound opens in the centre.</t>
+          <t>Tender H2: lift before frost and overwinter bright, frost-free and almost dry.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Green leaves with broad cream-yellow margins blush pink in autumn; yellow summer flowers.</t>
+          <t>Velvety green leaves develop burgundy margins and tips in strong light and cool weather.</t>
         </is>
       </c>
     </row>
@@ -2825,32 +2825,32 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Purple Fountain Grass 'Rubrum'</t>
+          <t>Sedum 'Atlantis'</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Pennisetum advena 'Rubrum'</t>
+          <t>Sedum takesimense 'Nonsitnal' (Atlantis)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Moderate during active growth; never leave waterlogged.</t>
+          <t>Low once established.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Tender H3: lift or pot before hard frost and overwinter frost-free; fleece alone is unreliable in Bromsgrove.</t>
+          <t>Cut back old flower stems in spring and divide if the mound opens in the centre.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Arching burgundy leaves and purple-brown bottlebrush plumes from summer into autumn.</t>
+          <t>Green leaves with broad cream-yellow margins blush pink in autumn; yellow summer flowers.</t>
         </is>
       </c>
     </row>
@@ -2862,32 +2862,32 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Ajuga 'Midnight Mystery'</t>
+          <t>Purple Fountain Grass 'Rubrum'</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Ajuga reptans 'Midnight Mystery'</t>
+          <t>Pennisetum advena 'Rubrum'</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Partial shade or gentle sun.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Moderate; keep moist while establishing.</t>
+          <t>Moderate during active growth; never leave waterlogged.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Remove unwanted runners and maintain airflow to reduce mildew.</t>
+          <t>Tender H3: lift or pot before hard frost and overwinter frost-free; fleece alone is unreliable in Bromsgrove.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Dark bronze evergreen foliage with contrasting rosy-pink spring flowers.</t>
+          <t>Arching burgundy leaves and purple-brown bottlebrush plumes from summer into autumn.</t>
         </is>
       </c>
     </row>
@@ -2899,32 +2899,32 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>New Zealand Flax (dark)</t>
+          <t>Ajuga 'Midnight Mystery'</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Phormium 'Platt's Black'</t>
+          <t>Ajuga reptans 'Midnight Mystery'</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade or gentle sun.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Moderate; drought-tolerant once established.</t>
+          <t>Moderate; keep moist while establishing.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Remove old leaves at base. Architectural and low-care.</t>
+          <t>Remove unwanted runners and maintain airflow to reduce mildew.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Evergreen dark foliage year-round.</t>
+          <t>Dark bronze evergreen foliage with contrasting rosy-pink spring flowers.</t>
         </is>
       </c>
     </row>
@@ -2936,69 +2936,69 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Agapanthus</t>
+          <t>New Zealand Flax (dark)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Agapanthus (species and cultivar unknown)</t>
+          <t>Phormium 'Platt's Black'</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Full sun for reliable flowering.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Low once established; water during establishment and prolonged late-summer drought.</t>
+          <t>Moderate; drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Grow in moisture-retentive but well-drained soil. Deadhead or retain seedheads deliberately and protect the crown in severe winter weather until hardiness is known.</t>
+          <t>Remove old leaves at base. Architectural and low-care.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Strap-shaped foliage photographed in August; flower colour and exact form remain unresolved.</t>
+          <t>Evergreen dark foliage year-round.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Patio</t>
+          <t>Stone Bed</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Honeysuckle</t>
+          <t>Agapanthus</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Lonicera</t>
+          <t>Agapanthus (species and cultivar unknown)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Sun, with shaded roots.</t>
+          <t>Full sun for reliable flowering.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Moderate.</t>
+          <t>Low once established; water during establishment and prolonged late-summer drought.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Light prune after flowering. Train onto support.</t>
+          <t>Grow in moisture-retentive but well-drained soil. Deadhead or retain seedheads deliberately and protect the crown in severe winter weather until hardiness is known.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Fragrant flowers June–August.</t>
+          <t>Strap-shaped foliage photographed in August; flower colour and exact form remain unresolved.</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Clematis</t>
+          <t>Honeysuckle</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Clematis montana</t>
+          <t>Lonicera</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3030,86 +3030,86 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Group 1 clematis — light prune after flowering only. Tie in new growth.</t>
+          <t>Light prune after flowering. Train onto support.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Sheets of pale pink flowers May; vigorous summer growth.</t>
+          <t>Fragrant flowers June–August.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Pear Tree</t>
+          <t>Clematis</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Pyrus</t>
+          <t>Clematis montana</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Sun, with shaded roots.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Deep watering in dry summers.</t>
+          <t>Moderate.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Winter prune for shape. Thin fruit if heavy.</t>
+          <t>Group 1 clematis — light prune after flowering only. Tie in new growth.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>White blossom April; fruit September; bare winter.</t>
+          <t>Sheets of pale pink flowers May; vigorous summer growth.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Big Pot 1</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia</t>
+          <t>Pear Tree</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia 'Mrs Popple'</t>
+          <t>Pyrus</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Keep compost moist. Water daily in hot weather.</t>
+          <t>Deep watering in dry summers.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
+          <t>Winter prune for shape. Thin fruit if heavy.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Red and purple pendant flowers June–October; deciduous in winter; new growth from the base in spring.</t>
+          <t>White blossom April; fruit September; bare winter.</t>
         </is>
       </c>
     </row>
@@ -3121,32 +3121,32 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Verbena</t>
+          <t>Fuchsia</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Verbena 'Showboat Light Pink'</t>
+          <t>Fuchsia 'Mrs Popple'</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out.</t>
+          <t>Keep compost moist. Water daily in hot weather.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to keep flowering. Tender annual — replace yearly.</t>
+          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Clusters of soft pink flowers June–October.</t>
+          <t>Red and purple pendant flowers June–October; deciduous in winter; new growth from the base in spring.</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3158,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa</t>
+          <t>Verbena</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa 'Cabaret Special Pink Star'</t>
+          <t>Verbena 'Showboat Light Pink'</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist. Hates drying out.</t>
+          <t>Regular; don't let compost dry out.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with liquid tomato food. Tender annual.</t>
+          <t>Deadhead to keep flowering. Tender annual — replace yearly.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Pink star-patterned flowers May–October. Continuous if fed.</t>
+          <t>Clusters of soft pink flowers June–October.</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Nepeta</t>
+          <t>Calibrachoa</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nepeta (catmint)</t>
+          <t>Calibrachoa 'Cabaret Special Pink Star'</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant once established.</t>
+          <t>Keep evenly moist. Hates drying out.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Cut back after first flush for a repeat. Aromatic — cats love it.</t>
+          <t>Feed weekly with liquid tomato food. Tender annual.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
+          <t>Pink star-patterned flowers May–October. Continuous if fed.</t>
         </is>
       </c>
     </row>
@@ -3232,32 +3232,32 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Lobelia</t>
+          <t>Nepeta</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
+          <t>Nepeta (catmint)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Keep moist at all times. Hates drying out.</t>
+          <t>Low to moderate. Drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Trim back leggy growth mid-season. Tender annual.</t>
+          <t>Cut back after first flush for a repeat. Aromatic — cats love it.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Deep blue and white trailing flowers May–October.</t>
+          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
         </is>
       </c>
     </row>
@@ -3269,69 +3269,69 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Lobelia</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Midnight Sky'</t>
+          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out completely.</t>
+          <t>Keep moist at all times. Hates drying out.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+          <t>Trim back leggy growth mid-season. Tender annual.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Dark purple-white trumpet flowers May–October.</t>
+          <t>Deep blue and white trailing flowers May–October.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Big Pot 2</t>
+          <t>Big Pot 1</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Lobelia</t>
+          <t>Petunia</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
+          <t>Petunia 'Midnight Sky'</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Keep moist at all times. Hates drying out.</t>
+          <t>Regular; don't let compost dry out completely.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Trim back leggy growth mid-season. Tender annual.</t>
+          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Deep blue and white trailing flowers May–October.</t>
+          <t>Dark purple-white trumpet flowers May–October.</t>
         </is>
       </c>
     </row>
@@ -3343,32 +3343,32 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Verbena</t>
+          <t>Lobelia</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Verbena 'Venturi Pink Bicolour'</t>
+          <t>Lobelia 'Waterfall Deep Blue Ice'</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out.</t>
+          <t>Keep moist at all times. Hates drying out.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to keep flowering. Tender annual.</t>
+          <t>Trim back leggy growth mid-season. Tender annual.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Pink bicolour flower clusters June–October.</t>
+          <t>Deep blue and white trailing flowers May–October.</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3380,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Verbena</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Sky Purple White Sky'</t>
+          <t>Verbena 'Venturi Pink Bicolour'</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out completely.</t>
+          <t>Regular; don't let compost dry out.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+          <t>Deadhead to keep flowering. Tender annual.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Purple-white striped trumpet flowers May–October.</t>
+          <t>Pink bicolour flower clusters June–October.</t>
         </is>
       </c>
     </row>
@@ -3417,12 +3417,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Nepeta</t>
+          <t>Petunia</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Nepeta (catmint)</t>
+          <t>Petunia 'Sky Purple White Sky'</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant once established.</t>
+          <t>Regular; don't let compost dry out completely.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Cut back after first flush for a repeat. Aromatic.</t>
+          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
+          <t>Purple-white striped trumpet flowers May–October.</t>
         </is>
       </c>
     </row>
@@ -3454,69 +3454,69 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia</t>
+          <t>Nepeta</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia 'Mrs Popple'</t>
+          <t>Nepeta (catmint)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Keep compost moist. Water daily in hot weather.</t>
+          <t>Low to moderate. Drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
+          <t>Cut back after first flush for a repeat. Aromatic.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Red and purple pendant flowers June–October; deciduous in winter.</t>
+          <t>Lavender-blue spikes June–September; grey-green aromatic foliage.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Little Pot 1</t>
+          <t>Big Pot 2</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Geranium</t>
+          <t>Fuchsia</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Pelargonium 'Trend Sophie Dark Red'</t>
+          <t>Fuchsia 'Mrs Popple'</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let compost dry slightly between waterings.</t>
+          <t>Keep compost moist. Water daily in hot weather.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Deadhead regularly. Feed fortnightly. Not frost-hardy — overwinter indoors or treat as annual.</t>
+          <t>Hardy bush fuchsia. Cut back hard in spring. Feed fortnightly through summer.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Dark red flower heads May–October; scented rounded leaves.</t>
+          <t>Red and purple pendant flowers June–October; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Geranium</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Vivini Blue Star'</t>
+          <t>Pelargonium 'Trend Sophie Dark Red'</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3543,34 +3543,34 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out completely.</t>
+          <t>Moderate. Let compost dry slightly between waterings.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+          <t>Deadhead regularly. Feed fortnightly. Not frost-hardy — overwinter indoors or treat as annual.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Blue-white star-patterned flowers May–October.</t>
+          <t>Dark red flower heads May–October; scented rounded leaves.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Little Pot 2</t>
+          <t>Little Pot 1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Coreopsis Gold</t>
+          <t>Petunia</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Coreopsis 'Gold'</t>
+          <t>Petunia 'Vivini Blue Star'</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3580,91 +3580,91 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Moderate; the small pot dries quickly, but avoid permanently wet compost.</t>
+          <t>Regular; don't let compost dry out completely.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Deadhead regularly for continuous flowering. Cut tired growth back by up to half for a second flush and keep the pot freely drained through winter.</t>
+          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Bright golden-yellow daisy flowers June–September above a compact leafy mound.</t>
+          <t>Blue-white star-patterned flowers May–October.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Cercis Pot</t>
+          <t>Little Pot 2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Cercis 'Carolina Sweetheart'</t>
+          <t>Coreopsis Gold</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Cercis canadensis 'Nccc1'</t>
+          <t>Coreopsis 'Gold'</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm position; shelter the pot from severe drying wind.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing. Water deeply when the upper compost starts to dry, without leaving the pot waterlogged.</t>
+          <t>Moderate; the small pot dries quickly, but avoid permanently wet compost.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Avoid routine pruning; remove only dead, damaged or crossing growth. Refresh the compost surface in spring and plan for a larger root run as the tree matures.</t>
+          <t>Deadhead regularly for continuous flowering. Cut tired growth back by up to half for a second flush and keep the pot freely drained through winter.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Heart-shaped leaves open maroon-red and mature through green, cream and pink variegation; bare branches may carry pink-purple flowers in spring as the tree matures.</t>
+          <t>Bright golden-yellow daisy flowers June–September above a compact leafy mound.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Front Pot</t>
+          <t>Cercis Pot</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Gazania 'Sunny Side Up'</t>
+          <t>Cercis 'Carolina Sweetheart'</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Gazania rigens 'Sunny Side Up'</t>
+          <t>Cercis canadensis 'Nccc1'</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Full sun. Flowers close in shade and on overcast days.</t>
+          <t>Full sun in a warm position; shelter the pot from severe drying wind.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant. Sharp drainage.</t>
+          <t>Keep evenly moist while establishing. Water deeply when the upper compost starts to dry, without leaving the pot waterlogged.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent flowers to encourage more. Tender annual — replace each year. Does not recover from frost.</t>
+          <t>Avoid routine pruning; remove only dead, damaged or crossing growth. Refresh the compost surface in spring and plan for a larger root run as the tree matures.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Large cream-white daisy flowers with contrasting dark centres May–October; closes at night and on dull days.</t>
+          <t>Heart-shaped leaves open maroon-red and mature through green, cream and pink variegation; bare branches may carry pink-purple flowers in spring as the tree matures.</t>
         </is>
       </c>
     </row>
@@ -3676,32 +3676,32 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Gazania 'Orange Flame'</t>
+          <t>Gazania 'Sunny Side Up'</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Gazania rigens 'Orange Flame'</t>
+          <t>Gazania rigens 'Sunny Side Up'</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Full sun. Flowers close in shade.</t>
+          <t>Full sun. Flowers close in shade and on overcast days.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant.</t>
+          <t>Low to moderate. Drought-tolerant. Sharp drainage.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to extend flowering. Tender annual — replace each year. Not frost-hardy.</t>
+          <t>Deadhead spent flowers to encourage more. Tender annual — replace each year. Does not recover from frost.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Vivid orange flame-patterned daisy flowers May–October; closes at night and on dull days.</t>
+          <t>Large cream-white daisy flowers with contrasting dark centres May–October; closes at night and on dull days.</t>
         </is>
       </c>
     </row>
@@ -3713,32 +3713,32 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa</t>
+          <t>Gazania 'Orange Flame'</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa spp.</t>
+          <t>Gazania rigens 'Orange Flame'</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun. Flowers close in shade.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist. Hates drying out.</t>
+          <t>Low to moderate. Drought-tolerant.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with liquid tomato food. Self-cleaning — no deadheading needed. Tender annual.</t>
+          <t>Deadhead to extend flowering. Tender annual — replace each year. Not frost-hardy.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Masses of small petunia-like flowers May–October. Continuous if fed.</t>
+          <t>Vivid orange flame-patterned daisy flowers May–October; closes at night and on dull days.</t>
         </is>
       </c>
     </row>
@@ -3750,143 +3750,143 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Bacopa White</t>
+          <t>Calibrachoa</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Sutera cordata (white cultivar)</t>
+          <t>Calibrachoa spp.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist.</t>
+          <t>Keep evenly moist. Hates drying out.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
+          <t>Feed weekly with liquid tomato food. Self-cleaning — no deadheading needed. Tender annual.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Tiny white flowers May–October; neat trailing habit.</t>
+          <t>Masses of small petunia-like flowers May–October. Continuous if fed.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Wall Pot 1</t>
+          <t>Front Pot</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Candy House Mix</t>
+          <t>Bacopa White</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa 'Candy House Mix'</t>
+          <t>Sutera cordata (white cultivar)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Regular; do not let dry out. Water at the base.</t>
+          <t>Keep evenly moist.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with liquid tomato food. Deadhead spent flowers. Tender annual — replace each season. Trim back if leggy to encourage bushy growth.</t>
+          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Prolific trailing flowers in mixed red, yellow and pink June–October; dies with first frost.</t>
+          <t>Tiny white flowers May–October; neat trailing habit.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Wall Pot 2</t>
+          <t>Wall Pot 1</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Echinacea 'Mooodz Glory'</t>
+          <t>Candy House Mix</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Echinacea 'Hilmooglor'</t>
+          <t>Calibrachoa 'Candy House Mix'</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Full sun for strongest flowering; tolerates partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Water thoroughly, then let the upper compost begin to dry; never leave the crown in cold, wet compost.</t>
+          <t>Regular; do not let dry out. Water at the base.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Deadhead fading flowers for further blooms, or retain selected cones for winter structure. Protect the pot from prolonged winter saturation.</t>
+          <t>Feed weekly with liquid tomato food. Deadhead spent flowers. Tender annual — replace each season. Trim back if leggy to encourage bushy growth.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>White, slightly drooping petals around golden-green cones from summer into autumn; dies back to a hardy crown in winter.</t>
+          <t>Prolific trailing flowers in mixed red, yellow and pink June–October; dies with first frost.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Wall Pot 2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Trailing Fuchsia</t>
+          <t>Echinacea 'Mooodz Glory'</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia (trailing cultivar)</t>
+          <t>Echinacea 'Hilmooglor'</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun for strongest flowering; tolerates partial shade.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Daily in hot weather; never let dry out completely.</t>
+          <t>Moderate. Water thoroughly, then let the upper compost begin to dry; never leave the crown in cold, wet compost.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly. Deadhead spent flowers. Not frost-hardy — replace each year.</t>
+          <t>Deadhead fading flowers for further blooms, or retain selected cones for winter structure. Protect the pot from prolonged winter saturation.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Pendant bicolour flowers June–October.</t>
+          <t>White, slightly drooping petals around golden-green cones from summer into autumn; dies back to a hardy crown in winter.</t>
         </is>
       </c>
     </row>
@@ -3898,32 +3898,32 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Bacopa</t>
+          <t>Trailing Fuchsia</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Sutera cordata</t>
+          <t>Fuchsia (trailing cultivar)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist.</t>
+          <t>Daily in hot weather; never let dry out completely.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
+          <t>Feed weekly. Deadhead spent flowers. Not frost-hardy — replace each year.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Tiny white flowers May–October; neat trailing habit.</t>
+          <t>Pendant bicolour flowers June–October.</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Trailing Lobelia</t>
+          <t>Bacopa</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Lobelia erinus (trailing)</t>
+          <t>Sutera cordata</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Keep moist; hates drying out.</t>
+          <t>Keep evenly moist.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Trim back mid-season if it gets straggly. Tender annual.</t>
+          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Blue trailing flowers May–October.</t>
+          <t>Tiny white flowers May–October; neat trailing habit.</t>
         </is>
       </c>
     </row>
@@ -3972,32 +3972,32 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Trailing Verbena</t>
+          <t>Trailing Lobelia</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Verbena (trailing cultivar)</t>
+          <t>Lobelia erinus (trailing)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let dry out.</t>
+          <t>Keep moist; hates drying out.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to extend flowering. Tender annual.</t>
+          <t>Trim back mid-season if it gets straggly. Tender annual.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Clusters of flowers June–October.</t>
+          <t>Blue trailing flowers May–October.</t>
         </is>
       </c>
     </row>
@@ -4009,69 +4009,69 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Trailing Verbena</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Petunia (cultivar unknown)</t>
+          <t>Verbena (trailing cultivar)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Check daily in warm weather; water thoroughly before the basket dries out.</t>
+          <t>Regular; don't let dry out.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly during flowering and remove faded blooms and seed capsules. Trim bare stems back to leafy growth.</t>
+          <t>Deadhead to extend flowering. Tender annual.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Funnel-shaped summer flowers from June until the first frost; cultivar unresolved.</t>
+          <t>Clusters of flowers June–October.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 1</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea</t>
+          <t>Petunia</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea macrophylla</t>
+          <t>Petunia (cultivar unknown)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Morning sun, afternoon shade.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Thirsty — water well in dry spells.</t>
+          <t>Check daily in warm weather; water thoroughly before the basket dries out.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
+          <t>Feed weekly during flowering and remove faded blooms and seed capsules. Trim bare stems back to leafy growth.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Mophead flowers July–Sept; bare in winter.</t>
+          <t>Funnel-shaped summer flowers from June until the first frost; cultivar unresolved.</t>
         </is>
       </c>
     </row>
@@ -4083,69 +4083,69 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Hydrangea</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Lavandula angustifolia</t>
+          <t>Hydrangea macrophylla</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Morning sun, afternoon shade.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Drought-tolerant.</t>
+          <t>Thirsty — water well in dry spells.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
+          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Purple spikes June–Aug; aromatic year-round.</t>
+          <t>Mophead flowers July–Sept; bare in winter.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 1</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Inferno'</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Inferno'</t>
+          <t>Lavandula angustifolia</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Avoid waterlogged soil.</t>
+          <t>Drought-tolerant.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
+          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
+          <t>Purple spikes June–Aug; aromatic year-round.</t>
         </is>
       </c>
     </row>
@@ -4157,32 +4157,32 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Pina Colada'</t>
+          <t>Coprosma 'Inferno'</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Pina Colada'</t>
+          <t>Coprosma 'Inferno'</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
+          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Let the soil drain between waterings.</t>
+          <t>Moderate while establishing. Avoid waterlogged soil.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
+          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
+          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
         </is>
       </c>
     </row>
@@ -4194,32 +4194,32 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'City Knights'</t>
+          <t>Coprosma 'Pina Colada'</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'City Knights'</t>
+          <t>Coprosma 'Pina Colada'</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
+          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
+          <t>Moderate while establishing. Let the soil drain between waterings.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
+          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
+          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
         </is>
       </c>
     </row>
@@ -4231,32 +4231,32 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Kiwi' (Horopito)</t>
+          <t>Coprosma 'City Knights'</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Kiwi'</t>
+          <t>Coprosma 'City Knights'</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
+          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
+          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
+          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
         </is>
       </c>
     </row>
@@ -4268,69 +4268,69 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Polemonium 'Golden Feathers'</t>
+          <t>Hebe 'Kiwi' (Horopito)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Polemonium 'Golden Feathers'</t>
+          <t>Hebe 'Kiwi'</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
+          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
+          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
+          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Climbing Rose 'Super Fairy'</t>
+          <t>Polemonium 'Golden Feathers'</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Helsufair'</t>
+          <t>Polemonium 'Golden Feathers'</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Sun to light partial shade.</t>
+          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base in dry spells, especially while establishing.</t>
+          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
+          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
+          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
         </is>
       </c>
     </row>
@@ -4342,32 +4342,32 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Variegated Dogwood</t>
+          <t>Climbing Rose 'Super Fairy'</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Cornus alba 'Elegantissima'</t>
+          <t>Rosa 'Helsufair'</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
+          <t>Sun to light partial shade.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
+          <t>Deep water at the base in dry spells, especially while establishing.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
+          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
+          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -4379,32 +4379,32 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Red Hot Poker</t>
+          <t>Variegated Dogwood</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Kniphofia</t>
+          <t>Cornus alba 'Elegantissima'</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the strongest flowering.</t>
+          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
+          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
+          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
+          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
         </is>
       </c>
     </row>
@@ -4416,32 +4416,32 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Leucothoe 'Little Flames'</t>
+          <t>Red Hot Poker</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Leucothoe 'Little Flames'</t>
+          <t>Kniphofia</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
+          <t>Full sun for the strongest flowering.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
+          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
+          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
+          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
         </is>
       </c>
     </row>
@@ -4453,69 +4453,69 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Rose (pink)</t>
+          <t>Leucothoe 'Little Flames'</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Rosa — IDENTIFY</t>
+          <t>Leucothoe 'Little Flames'</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Sun.</t>
+          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Deep watering, mulch in spring.</t>
+          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Prune late winter; deadhead through summer.</t>
+          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Flowers June–Sept; bare winter.</t>
+          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Photinia (existing canopy)</t>
+          <t>Rose (pink)</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Photinia (cultivar to confirm)</t>
+          <t>Rosa — IDENTIFY</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Sun.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Water deeply only in prolonged dry periods once established.</t>
+          <t>Deep watering, mulch in spring.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
+          <t>Prune late winter; deadhead through summer.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
+          <t>Flowers June–Sept; bare winter.</t>
         </is>
       </c>
     </row>
@@ -4527,32 +4527,32 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>The Pilgrim</t>
+          <t>Photinia (existing canopy)</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Auswalker'</t>
+          <t>Photinia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base during dry spells, especially while establishing.</t>
+          <t>Water deeply only in prolonged dry periods once established.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
+          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
+          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
         </is>
       </c>
     </row>
@@ -4564,32 +4564,32 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>The Generous Gardener</t>
+          <t>The Pilgrim</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Ausdrawn'</t>
+          <t>Rosa 'Auswalker'</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
+          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base during dry spells, especially in its first two years.</t>
+          <t>Deep water at the base during dry spells, especially while establishing.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
+          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
+          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -4601,32 +4601,32 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 1 (2 × Little Devil)</t>
+          <t>The Generous Gardener</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Little Devil'</t>
+          <t>Rosa 'Ausdrawn'</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; foliage is darkest with good light.</t>
+          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Water both root balls deeply in dry spells for the first two growing seasons; then only during prolonged drought.</t>
+          <t>Deep water at the base during dry spells, especially in its first two years.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Treat as two compact deciduous ninebarks. Keep each crown distinct and remove a few oldest stems at ground level only once established; avoid clipping the cluster into one solid ball.</t>
+          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Burgundy-purple foliage spring to autumn; pale pinkish-white flowers in early summer; bare in winter.</t>
+          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
         </is>
       </c>
     </row>
@@ -4638,32 +4638,32 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 2 (2 × Lady in Red)</t>
+          <t>Physocarpus Cluster 1 (2 × Little Devil + 1 × Lady in Red)</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Lady in Red'</t>
+          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; best foliage colour in brighter light.</t>
+          <t>Sun to partial shade; foliage is darkest with good light.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Water both root balls deeply in dry spells while establishing; afterwards they are fairly drought tolerant.</t>
+          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Treat as two deciduous ninebarks. Keep their layered outlines distinct and remove a few oldest stems at the base in late winter only when congestion develops.</t>
+          <t>Keep all three crowns distinct, with the taller Lady in Red rising through the two compact Little Devils. Renew individual shrubs from the base only when mature and congested.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Fresh red foliage matures bronze-purple; pink flower clusters in summer; bare in winter.</t>
+          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
         </is>
       </c>
     </row>
@@ -4675,32 +4675,32 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 3 (2 × Little Devil + 1 × Lady in Red)</t>
+          <t>Physocarpus Cluster 2 (2 × Lady in Red + 1 × Little Devil)</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
+          <t>Physocarpus opulifolius 'Lady in Red' &amp; 'Little Devil'</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; brighter light strengthens the burgundy and red-bronze foliage.</t>
+          <t>Sun to partial shade; best foliage colour in brighter light.</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Water all three root balls deeply in dry spells while establishing; afterwards the cluster is fairly drought tolerant.</t>
+          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Keep the two lower Little Devils and taller Lady in Red readable as a layered trio. Renew individual shrubs from the base only when mature and congested; do not shear the cluster into one mass.</t>
+          <t>Keep the compact Little Devil readable against the two taller Lady in Reds. Remove a few oldest stems at the base only when congestion develops.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
+          <t>Red, bronze and burgundy foliage spring to autumn with pink flower clusters in summer; bare in winter.</t>
         </is>
       </c>
     </row>
@@ -4712,32 +4712,32 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Magic Carpet</t>
+          <t>Azalea japonica 'Silvester'</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Spiraea japonica 'Magic Carpet'</t>
+          <t>Rhododendron 'Sylvester'</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Sun to light partial shade; brighter light gives the strongest gold foliage.</t>
+          <t>Partial or dappled shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Water regularly during its first summer, then only in prolonged dry spells.</t>
+          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Lightly trim after flowering or cut back by about a third in early spring to encourage colourful new growth.</t>
+          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged or wayward growth.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Gold foliage with red young growth, deep-pink summer flowers and warm autumn colour; deciduous in winter.</t>
+          <t>Compact evergreen foliage with purple-pink flowers in late spring.</t>
         </is>
       </c>
     </row>
@@ -4749,32 +4749,32 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Purple Gem</t>
+          <t>Nemesia 'Lady Penelope'</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
+          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Shade to partial shade.</t>
+          <t>Full sun to light partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
+          <t>Dropper supplied. Keep evenly moist while flowering but never waterlogged.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
+          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
+          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
         </is>
       </c>
     </row>
@@ -4786,32 +4786,32 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Libretto'</t>
+          <t>Purple Gem</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Libretto'</t>
+          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
+          <t>Shade to partial shade.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
+          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
+          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
+          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
         </is>
       </c>
     </row>
@@ -4823,32 +4823,32 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Festuca 'Elijah Blue' (3 plants)</t>
+          <t>Rhododendron 'Libretto'</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Festuca glauca 'Elijah Blue'</t>
+          <t>Rhododendron 'Libretto'</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Water regularly during the first season; drought tolerant once established.</t>
+          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
+          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
+          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
         </is>
       </c>
     </row>
@@ -4860,32 +4860,32 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Pieris 'Polar Passion'</t>
+          <t>Festuca 'Elijah Blue' (3 plants)</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
+          <t>Festuca glauca 'Elijah Blue'</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
+          <t>Water regularly during the first season; drought tolerant once established.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
+          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
+          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
         </is>
       </c>
     </row>
@@ -4897,32 +4897,32 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Dahlia 'Tampico'</t>
+          <t>Pieris 'Polar Passion'</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
+          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Full sun, sheltered from strong wind.</t>
+          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
+          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
+          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
+          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Verbena 'Margaret's Memory'</t>
+          <t>Dahlia 'Tampico'</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Glandularia 'Margaret's Memory'</t>
+          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Full sun, sheltered from strong wind.</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
+          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
+          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
+          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
         </is>
       </c>
     </row>
@@ -4971,32 +4971,32 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Calluna Trio Mix (3 plants)</t>
+          <t>Verbena 'Margaret's Memory'</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris mixed cultivars</t>
+          <t>Glandularia 'Margaret's Memory'</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Full sun in an open position.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
+          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
+          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>A three-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
+          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
         </is>
       </c>
     </row>
@@ -5008,106 +5008,106 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Achillea</t>
+          <t>Calluna Trio Mix (3 plants)</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Achillea millefolium</t>
+          <t>Calluna vulgaris mixed cultivars</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun in an open position.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant once established.</t>
+          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
+          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
+          <t>A three-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Mexican Orange Blossom</t>
+          <t>Achillea</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Choisya ternata 'Sundance'</t>
+          <t>Achillea millefolium</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Sun for best colour.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Moderate.</t>
+          <t>Low to moderate. Drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Light prune after flowering to shape. Low-care.</t>
+          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
+          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Shrub Rose (cultivar to confirm)</t>
+          <t>Azalea japonica 'Lotte'</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Rosa (Shrub Group; cultivar to confirm)</t>
+          <t>Rhododendron 'Lotte'</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
+          <t>Partial or dappled shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
+          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
+          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged growth.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
+          <t>Compact glossy evergreen foliage with deep-pink flowers in late spring.</t>
         </is>
       </c>
     </row>
@@ -5119,32 +5119,32 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Bay Tree</t>
+          <t>Mexican Orange Blossom</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Laurus nobilis</t>
+          <t>Choisya ternata 'Sundance'</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Sun for best colour.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
+          <t>Moderate.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
+          <t>Light prune after flowering to shape. Low-care.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
+          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Japanese Skimmia</t>
+          <t>Shrub Rose (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica (cultivar and sex to confirm)</t>
+          <t>Rosa (Shrub Group; cultivar to confirm)</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
+          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
+          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
+          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
+          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
         </is>
       </c>
     </row>
@@ -5193,32 +5193,32 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Hardy Fuchsia (cultivar to confirm)</t>
+          <t>Bay Tree</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
+          <t>Laurus nobilis</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
+          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
+          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
+          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
         </is>
       </c>
     </row>
@@ -5230,32 +5230,32 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Clematis (cultivar to confirm)</t>
+          <t>Japanese Skimmia</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Clematis viticella (cultivar to confirm)</t>
+          <t>Skimmia japonica (cultivar and sex to confirm)</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade, with a cool shaded root run.</t>
+          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
+          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
+          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Deciduous climber with abundant summer flowers on new growth.</t>
+          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
         </is>
       </c>
     </row>
@@ -5267,32 +5267,32 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea 'Bloody Marie'</t>
+          <t>Hardy Fuchsia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea paniculata 'Bloody Marie'</t>
+          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
+          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
+          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
+          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
+          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5304,32 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Euphorbia 'Ascot Petite'</t>
+          <t>Clematis (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Euphorbia × martinii 'Ascot Petite'</t>
+          <t>Clematis viticella (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a sheltered position.</t>
+          <t>Sun to partial shade, with a cool shaded root run.</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
+          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
+          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
+          <t>Deciduous climber with abundant summer flowers on new growth.</t>
         </is>
       </c>
     </row>
@@ -5341,32 +5341,32 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Flaming Silver</t>
+          <t>Hydrangea 'Bloody Marie'</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Pieris japonica 'Flaming Silver'</t>
+          <t>Hydrangea paniculata 'Bloody Marie'</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
+          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
+          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
+          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
+          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Astrantia trio</t>
+          <t>Euphorbia 'Ascot Petite'</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
+          <t>Euphorbia × martinii 'Ascot Petite'</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Sun to light shade.</t>
+          <t>Full sun in a sheltered position.</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
+          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
+          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
+          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
         </is>
       </c>
     </row>
@@ -5415,32 +5415,32 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Pittosporum 'Tom Thumb'</t>
+          <t>Flaming Silver</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
+          <t>Pieris japonica 'Flaming Silver'</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
+          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
+          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
+          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Gaura 'Gaudi Red'</t>
+          <t>Astrantia trio</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
+          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Sun to light shade.</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
+          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
+          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
+          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
         </is>
       </c>
     </row>
@@ -5489,32 +5489,32 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Bell's Extra Special'</t>
+          <t>Pittosporum 'Tom Thumb'</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Erica carnea 'Bell's Extra Special'</t>
+          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
+          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
+          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
+          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
         </is>
       </c>
     </row>
@@ -5526,32 +5526,32 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Tib'</t>
+          <t>Gaura 'Gaudi Red'</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Tib'</t>
+          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Full sun for compact growth and the best flower display.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
+          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
+          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
+          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
         </is>
       </c>
     </row>
@@ -5563,32 +5563,32 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Bell Heather 'Providence' (2 plants)</t>
+          <t>Heather 'Bell's Extra Special'</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Daboecia cantabrica 'Providence'</t>
+          <t>Erica carnea 'Bell's Extra Special'</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
+          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
+          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
+          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
+          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
         </is>
       </c>
     </row>
@@ -5600,32 +5600,32 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Leprechaun'</t>
+          <t>Heather 'Tib'</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Leprechaun'</t>
+          <t>Calluna vulgaris 'Tib'</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the brightest foliage colour.</t>
+          <t>Full sun for compact growth and the best flower display.</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
+          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
+          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
+          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
         </is>
       </c>
     </row>
@@ -5637,32 +5637,32 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Winter Chocolate'</t>
+          <t>Bell Heather 'Providence' (2 plants)</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Winter Chocolate'</t>
+          <t>Daboecia cantabrica 'Providence'</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
+          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
+          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
+          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
+          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
         </is>
       </c>
     </row>
@@ -5674,32 +5674,32 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Ceratostigma</t>
+          <t>Heather 'Leprechaun'</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Ceratostigma plumbaginoides</t>
+          <t>Calluna vulgaris 'Leprechaun'</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
+          <t>Full sun for the brightest foliage colour.</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
+          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
+          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
+          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
         </is>
       </c>
     </row>
@@ -5711,32 +5711,32 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Hypericum (cultivar to confirm)</t>
+          <t>Heather 'Winter Chocolate'</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Hypericum (cultivar to confirm)</t>
+          <t>Calluna vulgaris 'Winter Chocolate'</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
+          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
+          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
+          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
+          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Bluebell Creeper</t>
+          <t>Ceratostigma</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
+          <t>Ceratostigma plumbaginoides</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a warm, sheltered position.</t>
+          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
+          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
+          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
+          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
         </is>
       </c>
     </row>
@@ -5785,32 +5785,32 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Rhubarb and Custard'</t>
+          <t>Hypericum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
+          <t>Hypericum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a warm, sheltered spot.</t>
+          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
+          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
+          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
+          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Salvia 'Salgoon Lake Blueberry'</t>
+          <t>Bluebell Creeper</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
+          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Full sun to partial shade in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
+          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
+          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
+          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
         </is>
       </c>
     </row>
@@ -5859,481 +5859,592 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Little Devil</t>
+          <t>Hebe 'Rhubarb and Custard'</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Little Devil'</t>
+          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; foliage is darkest with good light.</t>
+          <t>Full sun to partial shade in a warm, sheltered spot.</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Water deeply in dry spells for the first two growing seasons; then only during prolonged drought.</t>
+          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Compact deciduous ninebark. Remove a few of the oldest stems at ground level in late winter once established; avoid clipping into a tight ball.</t>
+          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Burgundy-purple foliage spring to autumn; pale pinkish-white flowers in early summer; bare in winter.</t>
+          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Front Stone Trough</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Salvia 'Salgoon Lake Blueberry'</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Part to full shade.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Keep moist; never bone-dry in the trough.</t>
+          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Watch for slugs/snails. Divide clumps in spring.</t>
+          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Fresh leaves spring; dies back over winter.</t>
+          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Front Box Hedge</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Wall Cotoneaster (species to confirm)</t>
+          <t>Fern 'Jurassic Gold'</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Cotoneaster (species to confirm)</t>
+          <t>Dryopteris wallichiana 'Hollasic' (Jurassic Gold)</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Sun to part shade.</t>
+          <t>Full shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
+          <t>Shares the existing sprinkler with location 10. Keep moist but well drained while establishing.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
+          <t>Mulch well over moist soil, keeping the crown clear. Remove dead or damaged fronds as needed and protect new croziers from late frost and slugs.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
+          <t>Rose-tinted young fronds mature through bright gold to green; deciduous to semi-evergreen depending on winter.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Front Stone Trough</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Mixed Pot</t>
+          <t>Hosta</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Mixed seasonal planting — contents to confirm</t>
+          <t>Hosta</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
+          <t>Part to full shade.</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
+          <t>Keep moist; never bone-dry in the trough.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
+          <t>Watch for slugs/snails. Divide clumps in spring.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
+          <t>Fresh leaves spring; dies back over winter.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Front Box Hedge</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia Pot</t>
+          <t>Wall Cotoneaster (species to confirm)</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia cultivars — identities to confirm</t>
+          <t>Cotoneaster (species to confirm)</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
+          <t>Sun to part shade.</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
+          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
+          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
+          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Apple Tree</t>
+          <t>Mixed Pot</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Malus domestica</t>
+          <t>Mixed seasonal planting — contents to confirm</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Water well in dry spells while fruiting.</t>
+          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
+          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Blossom April–May; fruit late summer–autumn.</t>
+          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Damson Tree</t>
+          <t>Fuchsia Pot</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
+          <t>Fuchsia cultivars — identities to confirm</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Full sun for reliable blossom and fruit ripening.</t>
+          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
+          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
+          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
+          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Front Gate Tree</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Weeping Crab Apple (cultivar to confirm)</t>
+          <t>Apple Tree</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
+          <t>Malus domestica</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
+          <t>Water well in dry spells while fruiting.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
+          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
+          <t>Blossom April–May; fruit late summer–autumn.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Kentia Palm</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Kentia Palm — assumed</t>
+          <t>Damson Tree</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Howea forsteriana</t>
+          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
+          <t>Full sun for reliable blossom and fruit ripening.</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
+          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
+          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
+          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Nemesia Pot</t>
+          <t>Front Gate Tree</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Lady Penelope'</t>
+          <t>Weeping Crab Apple (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
+          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade in a sheltered position.</t>
+          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Keep the container evenly moist but never waterlogged.</t>
+          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
+          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
+          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>House · Hallway · Kentia Palm</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Viburnum 'Lisarose'</t>
+          <t>Kentia Palm — assumed</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Viburnum tinus 'Lisarose'</t>
+          <t>Howea forsteriana</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Skimmia 'Cleopatra'</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>Skimmia Pot</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Hedera helix 'Yellow Ripple'</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Full shade to partial shade; shelter pale margins from scorching sun.</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Share the Skimmia's evenly moist, well-drained compost; check beneath the foliage before watering.</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Trim to keep the ivy within the pot and away from the Skimmia crown. Remove any all-green reverted shoots at their origin.</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen lobed leaves with yellow-to-cream margins provide year-round trailing colour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
           <t>Viburnum Pot</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus Spirit</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus 'Anvi' (Spirit)</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sun or partial shade, with shelter from cold drying winds.</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>Pink buds open to lightly fragrant creamy-white flowers from late winter into spring, followed by blue-black ornamental berries.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G159"/>
+  <autoFilter ref="A1:G162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$164</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6261,190 +6261,264 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>House · Sitting Room · ‘Gioia’ Fern</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Cleopatra'</t>
+          <t>Bird’s Nest Fern ‘Gioia’</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
+          <t>Asplenium antiquum ‘Gioia’</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
+          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
+          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
+          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>House · Hallway · Staghorn Fern</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Yellow Ripple'</t>
+          <t>Staghorn Fern</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
+          <t>Platycerium bifurcatum</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Full shade to partial shade; shelter pale margins from scorching sun.</t>
+          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Share the Skimmia's evenly moist, well-drained compost; check beneath the foliage before watering.</t>
+          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Trim to keep the ivy within the pot and away from the Skimmia crown. Remove any all-green reverted shoots at their origin.</t>
+          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Evergreen lobed leaves with yellow-to-cream margins provide year-round trailing colour.</t>
+          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Viburnum 'Lisarose'</t>
+          <t>Skimmia 'Cleopatra'</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Viburnum tinus 'Lisarose'</t>
+          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Hedera helix 'Yellow Ripple'</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+          <t>Full shade to partial shade; shelter pale margins from scorching sun.</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+          <t>Share the Skimmia's evenly moist, well-drained compost; check beneath the foliage before watering.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+          <t>Trim to keep the ivy within the pot and away from the Skimmia crown. Remove any all-green reverted shoots at their origin.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+          <t>Evergreen lobed leaves with yellow-to-cream margins provide year-round trailing colour.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
           <t>Viburnum Pot</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus Spirit</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus 'Anvi' (Spirit)</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sun or partial shade, with shelter from cold drying winds.</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>Pink buds open to lightly fragrant creamy-white flowers from late winter into spring, followed by blue-black ornamental berries.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G162"/>
+  <autoFilter ref="A1:G164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$170</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3528,49 +3528,49 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Geranium</t>
+          <t>Helleborus Ice N' Roses Bennotta</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Pelargonium 'Trend Sophie Dark Red'</t>
+          <t>Helleborus × glandorfensis 'COSEH 6600'</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to sun in a sheltered position.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let compost dry slightly between waterings.</t>
+          <t>Keep compost evenly moist but freely drained; do not leave the crown waterlogged.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Deadhead regularly. Feed fortnightly. Not frost-hardy — overwinter indoors or treat as annual.</t>
+          <t>Remove tired leaves and faded flower stems in spring. Wear gloves when handling, and raise the pot so winter rain drains freely.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Dark red flower heads May–October; scented rounded leaves.</t>
+          <t>Deep pink to red outward-facing flowers from winter into spring above evergreen foliage.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Little Pot 1</t>
+          <t>Little Pot 2</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Coreopsis Gold</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Petunia 'Vivini Blue Star'</t>
+          <t>Coreopsis 'Gold'</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3580,91 +3580,91 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let compost dry out completely.</t>
+          <t>Moderate; the small pot dries quickly, but avoid permanently wet compost.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent blooms. Feed weekly. Tender annual.</t>
+          <t>Deadhead regularly for continuous flowering. Cut tired growth back by up to half for a second flush and keep the pot freely drained through winter.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Blue-white star-patterned flowers May–October.</t>
+          <t>Bright golden-yellow daisy flowers June–September above a compact leafy mound.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Little Pot 2</t>
+          <t>Cercis Pot</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Coreopsis Gold</t>
+          <t>Cercis 'Carolina Sweetheart'</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Coreopsis 'Gold'</t>
+          <t>Cercis canadensis 'Nccc1'</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun in a warm position; shelter the pot from severe drying wind.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Moderate; the small pot dries quickly, but avoid permanently wet compost.</t>
+          <t>Keep evenly moist while establishing. Water deeply when the upper compost starts to dry, without leaving the pot waterlogged.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Deadhead regularly for continuous flowering. Cut tired growth back by up to half for a second flush and keep the pot freely drained through winter.</t>
+          <t>Avoid routine pruning; remove only dead, damaged or crossing growth. Refresh the compost surface in spring and plan for a larger root run as the tree matures.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Bright golden-yellow daisy flowers June–September above a compact leafy mound.</t>
+          <t>Heart-shaped leaves open maroon-red and mature through green, cream and pink variegation; bare branches may carry pink-purple flowers in spring as the tree matures.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Cercis Pot</t>
+          <t>Front Pot</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Cercis 'Carolina Sweetheart'</t>
+          <t>Gazania 'Sunny Side Up'</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Cercis canadensis 'Nccc1'</t>
+          <t>Gazania rigens 'Sunny Side Up'</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm position; shelter the pot from severe drying wind.</t>
+          <t>Full sun. Flowers close in shade and on overcast days.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing. Water deeply when the upper compost starts to dry, without leaving the pot waterlogged.</t>
+          <t>Low to moderate. Drought-tolerant. Sharp drainage.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Avoid routine pruning; remove only dead, damaged or crossing growth. Refresh the compost surface in spring and plan for a larger root run as the tree matures.</t>
+          <t>Deadhead spent flowers to encourage more. Tender annual — replace each year. Does not recover from frost.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Heart-shaped leaves open maroon-red and mature through green, cream and pink variegation; bare branches may carry pink-purple flowers in spring as the tree matures.</t>
+          <t>Large cream-white daisy flowers with contrasting dark centres May–October; closes at night and on dull days.</t>
         </is>
       </c>
     </row>
@@ -3676,32 +3676,32 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Gazania 'Sunny Side Up'</t>
+          <t>Gazania 'Orange Flame'</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Gazania rigens 'Sunny Side Up'</t>
+          <t>Gazania rigens 'Orange Flame'</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Full sun. Flowers close in shade and on overcast days.</t>
+          <t>Full sun. Flowers close in shade.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant. Sharp drainage.</t>
+          <t>Low to moderate. Drought-tolerant.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Deadhead spent flowers to encourage more. Tender annual — replace each year. Does not recover from frost.</t>
+          <t>Deadhead to extend flowering. Tender annual — replace each year. Not frost-hardy.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Large cream-white daisy flowers with contrasting dark centres May–October; closes at night and on dull days.</t>
+          <t>Vivid orange flame-patterned daisy flowers May–October; closes at night and on dull days.</t>
         </is>
       </c>
     </row>
@@ -3713,32 +3713,32 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Gazania 'Orange Flame'</t>
+          <t>Calibrachoa</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Gazania rigens 'Orange Flame'</t>
+          <t>Calibrachoa spp.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Full sun. Flowers close in shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant.</t>
+          <t>Keep evenly moist. Hates drying out.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to extend flowering. Tender annual — replace each year. Not frost-hardy.</t>
+          <t>Feed weekly with liquid tomato food. Self-cleaning — no deadheading needed. Tender annual.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Vivid orange flame-patterned daisy flowers May–October; closes at night and on dull days.</t>
+          <t>Masses of small petunia-like flowers May–October. Continuous if fed.</t>
         </is>
       </c>
     </row>
@@ -3750,143 +3750,143 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa</t>
+          <t>Bacopa White</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa spp.</t>
+          <t>Sutera cordata (white cultivar)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist. Hates drying out.</t>
+          <t>Keep evenly moist.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with liquid tomato food. Self-cleaning — no deadheading needed. Tender annual.</t>
+          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Masses of small petunia-like flowers May–October. Continuous if fed.</t>
+          <t>Tiny white flowers May–October; neat trailing habit.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Front Pot</t>
+          <t>Wall Pot 1</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Bacopa White</t>
+          <t>Phormium 'Flamingo'</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Sutera cordata (white cultivar)</t>
+          <t>Phormium 'Flamingo'</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun for strongest foliage colour; shelter from severe cold wind.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist.</t>
+          <t>Water while establishing, then let the upper compost dry slightly; never leave the pot waterlogged.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
+          <t>Remove only damaged leaves at the base. Raise the pot for winter drainage and protect the crown during severe frost.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Tiny white flowers May–October; neat trailing habit.</t>
+          <t>Evergreen, pink-striped sword-like leaves give year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Wall Pot 1</t>
+          <t>Wall Pot 2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Candy House Mix</t>
+          <t>Echinacea 'Mooodz Glory'</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Calibrachoa 'Candy House Mix'</t>
+          <t>Echinacea 'Hilmooglor'</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun for strongest flowering; tolerates partial shade.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Regular; do not let dry out. Water at the base.</t>
+          <t>Moderate. Water thoroughly, then let the upper compost begin to dry; never leave the crown in cold, wet compost.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly with liquid tomato food. Deadhead spent flowers. Tender annual — replace each season. Trim back if leggy to encourage bushy growth.</t>
+          <t>Deadhead fading flowers for further blooms, or retain selected cones for winter structure. Protect the pot from prolonged winter saturation.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Prolific trailing flowers in mixed red, yellow and pink June–October; dies with first frost.</t>
+          <t>White, slightly drooping petals around golden-green cones from summer into autumn; dies back to a hardy crown in winter.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Wall Pot 2</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Echinacea 'Mooodz Glory'</t>
+          <t>Trailing Fuchsia</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Echinacea 'Hilmooglor'</t>
+          <t>Fuchsia (trailing cultivar)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Full sun for strongest flowering; tolerates partial shade.</t>
+          <t>Partial shade to full sun.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Water thoroughly, then let the upper compost begin to dry; never leave the crown in cold, wet compost.</t>
+          <t>Daily in hot weather; never let dry out completely.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Deadhead fading flowers for further blooms, or retain selected cones for winter structure. Protect the pot from prolonged winter saturation.</t>
+          <t>Feed weekly. Deadhead spent flowers. Not frost-hardy — replace each year.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>White, slightly drooping petals around golden-green cones from summer into autumn; dies back to a hardy crown in winter.</t>
+          <t>Pendant bicolour flowers June–October.</t>
         </is>
       </c>
     </row>
@@ -3898,32 +3898,32 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Trailing Fuchsia</t>
+          <t>Bacopa</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia (trailing cultivar)</t>
+          <t>Sutera cordata</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Daily in hot weather; never let dry out completely.</t>
+          <t>Keep evenly moist.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly. Deadhead spent flowers. Not frost-hardy — replace each year.</t>
+          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Pendant bicolour flowers June–October.</t>
+          <t>Tiny white flowers May–October; neat trailing habit.</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Bacopa</t>
+          <t>Trailing Lobelia</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Sutera cordata</t>
+          <t>Lobelia erinus (trailing)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist.</t>
+          <t>Keep moist; hates drying out.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
+          <t>Trim back mid-season if it gets straggly. Tender annual.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Tiny white flowers May–October; neat trailing habit.</t>
+          <t>Blue trailing flowers May–October.</t>
         </is>
       </c>
     </row>
@@ -3972,32 +3972,32 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Trailing Lobelia</t>
+          <t>Trailing Verbena</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Lobelia erinus (trailing)</t>
+          <t>Verbena (trailing cultivar)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Keep moist; hates drying out.</t>
+          <t>Regular; don't let dry out.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Trim back mid-season if it gets straggly. Tender annual.</t>
+          <t>Deadhead to extend flowering. Tender annual.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Blue trailing flowers May–October.</t>
+          <t>Clusters of flowers June–October.</t>
         </is>
       </c>
     </row>
@@ -4009,32 +4009,32 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Trailing Verbena</t>
+          <t>Petunia</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Verbena (trailing cultivar)</t>
+          <t>Petunia (cultivar unknown)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let dry out.</t>
+          <t>Check daily in warm weather; water thoroughly before the basket dries out.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to extend flowering. Tender annual.</t>
+          <t>Feed weekly during flowering and remove faded blooms and seed capsules. Trim bare stems back to leafy growth.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Clusters of flowers June–October.</t>
+          <t>Funnel-shaped summer flowers from June until the first frost; cultivar unresolved.</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Calluna Trio Mix (2 plants)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Petunia (cultivar unknown)</t>
+          <t>Calluna vulgaris mixed cultivars</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4061,239 +4061,239 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Check daily in warm weather; water thoroughly before the basket dries out.</t>
+          <t>Keep compost lightly moist while establishing; never waterlog.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly during flowering and remove faded blooms and seed capsules. Trim bare stems back to leafy growth.</t>
+          <t>Use free-draining, preferably ericaceous compost. Trim lightly after flowering, never into bare wood.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Funnel-shaped summer flowers from June until the first frost; cultivar unresolved.</t>
+          <t>Evergreen foliage and late-summer to autumn colour.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 1</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea</t>
+          <t>Viola 'Rocky Purple Picotee' (2 plants)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea macrophylla</t>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Morning sun, afternoon shade.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Thirsty — water well in dry spells.</t>
+          <t>Keep compost evenly moist, particularly in windy weather.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
+          <t>Deadhead faded flowers and seed pods to extend the display.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Mophead flowers July–Sept; bare in winter.</t>
+          <t>Purple flowers with a pale picotee edge through the cool season.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 1</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Hedera helix 'Yellow Ripple' (2 plants)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Lavandula angustifolia</t>
+          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Shade to sun; avoid prolonged scorching sun on pale foliage.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Drought-tolerant.</t>
+          <t>Keep the shared basket compost evenly moist and well drained.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
+          <t>Trim trails to shape and keep stems clear of neighbouring crowns.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Purple spikes June–Aug; aromatic year-round.</t>
+          <t>Evergreen variegated trails give structure through winter.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Inferno'</t>
+          <t>Pansy 'Fire' (2 plants)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Inferno'</t>
+          <t>Viola × wittrockiana 'Fire'</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Avoid waterlogged soil.</t>
+          <t>Keep evenly moist but never saturated.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
+          <t>Remove faded flowers and seed pods regularly.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
+          <t>Cool-season flowers provide autumn-to-spring colour.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Pina Colada'</t>
+          <t>Pansy 'Rose Surprise' (2 plants)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Pina Colada'</t>
+          <t>Viola × wittrockiana 'Rose Surprise'</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Let the soil drain between waterings.</t>
+          <t>Keep evenly moist but never saturated.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
+          <t>Remove faded flowers and seed pods regularly.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
+          <t>Cool-season flowers provide autumn-to-spring colour.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 1</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'City Knights'</t>
+          <t>Hydrangea</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'City Knights'</t>
+          <t>Hydrangea macrophylla</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
+          <t>Morning sun, afternoon shade.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
+          <t>Thirsty — water well in dry spells.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
+          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
+          <t>Mophead flowers July–Sept; bare in winter.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 1</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Kiwi' (Horopito)</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Kiwi'</t>
+          <t>Lavandula angustifolia</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
+          <t>Drought-tolerant.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
+          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
+          <t>Purple spikes June–Aug; aromatic year-round.</t>
         </is>
       </c>
     </row>
@@ -4305,180 +4305,180 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Polemonium 'Golden Feathers'</t>
+          <t>Coprosma 'Inferno'</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Polemonium 'Golden Feathers'</t>
+          <t>Coprosma 'Inferno'</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
+          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
+          <t>Moderate while establishing. Avoid waterlogged soil.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
+          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
+          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Climbing Rose 'Super Fairy'</t>
+          <t>Coprosma 'Pina Colada'</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Helsufair'</t>
+          <t>Coprosma 'Pina Colada'</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Sun to light partial shade.</t>
+          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base in dry spells, especially while establishing.</t>
+          <t>Moderate while establishing. Let the soil drain between waterings.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
+          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
+          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Variegated Dogwood</t>
+          <t>Coprosma 'City Knights'</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Cornus alba 'Elegantissima'</t>
+          <t>Coprosma 'City Knights'</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
+          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
+          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
+          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
+          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Red Hot Poker</t>
+          <t>Hebe 'Kiwi' (Horopito)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Kniphofia</t>
+          <t>Hebe 'Kiwi'</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the strongest flowering.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
+          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
+          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
+          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Leucothoe 'Little Flames'</t>
+          <t>Polemonium 'Golden Feathers'</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Leucothoe 'Little Flames'</t>
+          <t>Polemonium 'Golden Feathers'</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
+          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
+          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
+          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
+          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
         </is>
       </c>
     </row>
@@ -4490,180 +4490,180 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Rose (pink)</t>
+          <t>Climbing Rose 'Super Fairy'</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Rosa — IDENTIFY</t>
+          <t>Rosa 'Helsufair'</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Sun.</t>
+          <t>Sun to light partial shade.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Deep watering, mulch in spring.</t>
+          <t>Deep water at the base in dry spells, especially while establishing.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Prune late winter; deadhead through summer.</t>
+          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Flowers June–Sept; bare winter.</t>
+          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Photinia (existing canopy)</t>
+          <t>Variegated Dogwood</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Photinia (cultivar to confirm)</t>
+          <t>Cornus alba 'Elegantissima'</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Water deeply only in prolonged dry periods once established.</t>
+          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
+          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
+          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>The Pilgrim</t>
+          <t>Red Hot Poker</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Auswalker'</t>
+          <t>Kniphofia</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
+          <t>Full sun for the strongest flowering.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base during dry spells, especially while establishing.</t>
+          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
+          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
+          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>The Generous Gardener</t>
+          <t>Leucothoe 'Little Flames'</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Ausdrawn'</t>
+          <t>Leucothoe 'Little Flames'</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
+          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base during dry spells, especially in its first two years.</t>
+          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
+          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
+          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 1 (2 × Little Devil + 1 × Lady in Red)</t>
+          <t>Rose (pink)</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
+          <t>Rosa — IDENTIFY</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; foliage is darkest with good light.</t>
+          <t>Sun.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
+          <t>Deep watering, mulch in spring.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Keep all three crowns distinct, with the taller Lady in Red rising through the two compact Little Devils. Renew individual shrubs from the base only when mature and congested.</t>
+          <t>Prune late winter; deadhead through summer.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
+          <t>Flowers June–Sept; bare winter.</t>
         </is>
       </c>
     </row>
@@ -4675,32 +4675,32 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 2 (2 × Lady in Red + 1 × Little Devil)</t>
+          <t>Photinia (existing canopy)</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Lady in Red' &amp; 'Little Devil'</t>
+          <t>Photinia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; best foliage colour in brighter light.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
+          <t>Water deeply only in prolonged dry periods once established.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Keep the compact Little Devil readable against the two taller Lady in Reds. Remove a few oldest stems at the base only when congestion develops.</t>
+          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Red, bronze and burgundy foliage spring to autumn with pink flower clusters in summer; bare in winter.</t>
+          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
         </is>
       </c>
     </row>
@@ -4712,32 +4712,32 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Azalea japonica 'Silvester'</t>
+          <t>The Pilgrim</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Sylvester'</t>
+          <t>Rosa 'Auswalker'</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Partial or dappled shade in a sheltered position.</t>
+          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
+          <t>Deep water at the base during dry spells, especially while establishing.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged or wayward growth.</t>
+          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Compact evergreen foliage with purple-pink flowers in late spring.</t>
+          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -4749,32 +4749,32 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Lady Penelope'</t>
+          <t>The Generous Gardener</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
+          <t>Rosa 'Ausdrawn'</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade in a sheltered position.</t>
+          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep evenly moist while flowering but never waterlogged.</t>
+          <t>Deep water at the base during dry spells, especially in its first two years.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
+          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
+          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
         </is>
       </c>
     </row>
@@ -4786,32 +4786,32 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Purple Gem</t>
+          <t>Physocarpus Cluster 1 (2 × Little Devil + 1 × Lady in Red)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
+          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Shade to partial shade.</t>
+          <t>Sun to partial shade; foliage is darkest with good light.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
+          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
+          <t>Keep all three crowns distinct, with the taller Lady in Red rising through the two compact Little Devils. Renew individual shrubs from the base only when mature and congested.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
+          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
         </is>
       </c>
     </row>
@@ -4823,32 +4823,32 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Libretto'</t>
+          <t>Physocarpus Cluster 2 (2 × Lady in Red + 1 × Little Devil)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Libretto'</t>
+          <t>Physocarpus opulifolius 'Lady in Red' &amp; 'Little Devil'</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
+          <t>Sun to partial shade; best foliage colour in brighter light.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
+          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
+          <t>Keep the compact Little Devil readable against the two taller Lady in Reds. Remove a few oldest stems at the base only when congestion develops.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
+          <t>Red, bronze and burgundy foliage spring to autumn with pink flower clusters in summer; bare in winter.</t>
         </is>
       </c>
     </row>
@@ -4860,32 +4860,32 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Festuca 'Elijah Blue' (3 plants)</t>
+          <t>Azalea japonica 'Silvester'</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Festuca glauca 'Elijah Blue'</t>
+          <t>Rhododendron 'Sylvester'</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Partial or dappled shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Water regularly during the first season; drought tolerant once established.</t>
+          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
+          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged or wayward growth.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
+          <t>Compact evergreen foliage with purple-pink flowers in late spring.</t>
         </is>
       </c>
     </row>
@@ -4897,32 +4897,32 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Pieris 'Polar Passion'</t>
+          <t>Nemesia 'Lady Penelope'</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
+          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
+          <t>Full sun to light partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
+          <t>Dropper supplied. Keep evenly moist while flowering but never waterlogged.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
+          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
+          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Dahlia 'Tampico'</t>
+          <t>Purple Gem</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
+          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Full sun, sheltered from strong wind.</t>
+          <t>Shade to partial shade.</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
+          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
+          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
+          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
         </is>
       </c>
     </row>
@@ -4971,32 +4971,32 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Verbena 'Margaret's Memory'</t>
+          <t>Rhododendron 'Libretto'</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Glandularia 'Margaret's Memory'</t>
+          <t>Rhododendron 'Libretto'</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
+          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
+          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
+          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
         </is>
       </c>
     </row>
@@ -5008,32 +5008,32 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Calluna Trio Mix (3 plants)</t>
+          <t>Festuca 'Elijah Blue' (3 plants)</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris mixed cultivars</t>
+          <t>Festuca glauca 'Elijah Blue'</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Full sun in an open position.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
+          <t>Water regularly during the first season; drought tolerant once established.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
+          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>A three-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
+          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
         </is>
       </c>
     </row>
@@ -5045,32 +5045,32 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Achillea</t>
+          <t>Pieris 'Polar Passion'</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Achillea millefolium</t>
+          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant once established.</t>
+          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
+          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
+          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
         </is>
       </c>
     </row>
@@ -5082,180 +5082,180 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Azalea japonica 'Lotte'</t>
+          <t>Dahlia 'Tampico'</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Lotte'</t>
+          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Partial or dappled shade in a sheltered position.</t>
+          <t>Full sun, sheltered from strong wind.</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
+          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged growth.</t>
+          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Compact glossy evergreen foliage with deep-pink flowers in late spring.</t>
+          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Mexican Orange Blossom</t>
+          <t>Verbena 'Margaret's Memory'</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Choisya ternata 'Sundance'</t>
+          <t>Glandularia 'Margaret's Memory'</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Sun for best colour.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Moderate.</t>
+          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Light prune after flowering to shape. Low-care.</t>
+          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
+          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Shrub Rose (cultivar to confirm)</t>
+          <t>Calluna Trio Mix (2 plants)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Rosa (Shrub Group; cultivar to confirm)</t>
+          <t>Calluna vulgaris mixed cultivars</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
+          <t>Full sun in an open position.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
+          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
+          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
+          <t>A two-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Bay Tree</t>
+          <t>Achillea</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Laurus nobilis</t>
+          <t>Achillea millefolium</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
+          <t>Low to moderate. Drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
+          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
+          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Japanese Skimmia</t>
+          <t>Azalea japonica 'Lotte'</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica (cultivar and sex to confirm)</t>
+          <t>Rhododendron 'Lotte'</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
+          <t>Partial or dappled shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
+          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
+          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged growth.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
+          <t>Compact glossy evergreen foliage with deep-pink flowers in late spring.</t>
         </is>
       </c>
     </row>
@@ -5267,32 +5267,32 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Hardy Fuchsia (cultivar to confirm)</t>
+          <t>Mexican Orange Blossom</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
+          <t>Choisya ternata 'Sundance'</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
+          <t>Sun for best colour.</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
+          <t>Moderate.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
+          <t>Light prune after flowering to shape. Low-care.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
+          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5304,32 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Clematis (cultivar to confirm)</t>
+          <t>Shrub Rose (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Clematis viticella (cultivar to confirm)</t>
+          <t>Rosa (Shrub Group; cultivar to confirm)</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade, with a cool shaded root run.</t>
+          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
+          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
+          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Deciduous climber with abundant summer flowers on new growth.</t>
+          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
         </is>
       </c>
     </row>
@@ -5341,32 +5341,32 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea 'Bloody Marie'</t>
+          <t>Bay Tree</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea paniculata 'Bloody Marie'</t>
+          <t>Laurus nobilis</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
+          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
+          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
+          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Euphorbia 'Ascot Petite'</t>
+          <t>Japanese Skimmia</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Euphorbia × martinii 'Ascot Petite'</t>
+          <t>Skimmia japonica (cultivar and sex to confirm)</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a sheltered position.</t>
+          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
+          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
+          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
+          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
         </is>
       </c>
     </row>
@@ -5415,32 +5415,32 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Flaming Silver</t>
+          <t>Hardy Fuchsia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Pieris japonica 'Flaming Silver'</t>
+          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
+          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
+          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
+          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
+          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Astrantia trio</t>
+          <t>Clematis (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
+          <t>Clematis viticella (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Sun to light shade.</t>
+          <t>Sun to partial shade, with a cool shaded root run.</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
+          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
+          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
+          <t>Deciduous climber with abundant summer flowers on new growth.</t>
         </is>
       </c>
     </row>
@@ -5489,32 +5489,32 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Pittosporum 'Tom Thumb'</t>
+          <t>Hydrangea 'Bloody Marie'</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
+          <t>Hydrangea paniculata 'Bloody Marie'</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
+          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
+          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
+          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -5526,32 +5526,32 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Gaura 'Gaudi Red'</t>
+          <t>Euphorbia 'Ascot Petite'</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
+          <t>Euphorbia × martinii 'Ascot Petite'</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Full sun in a sheltered position.</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
+          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
+          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
+          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
         </is>
       </c>
     </row>
@@ -5563,32 +5563,32 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Bell's Extra Special'</t>
+          <t>Flaming Silver</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Erica carnea 'Bell's Extra Special'</t>
+          <t>Pieris japonica 'Flaming Silver'</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
+          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
+          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
+          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
+          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
         </is>
       </c>
     </row>
@@ -5600,32 +5600,32 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Tib'</t>
+          <t>Astrantia trio</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Tib'</t>
+          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Full sun for compact growth and the best flower display.</t>
+          <t>Sun to light shade.</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
+          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
+          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
+          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
         </is>
       </c>
     </row>
@@ -5637,32 +5637,32 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Bell Heather 'Providence' (2 plants)</t>
+          <t>Pittosporum 'Tom Thumb'</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Daboecia cantabrica 'Providence'</t>
+          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
+          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
+          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
+          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
         </is>
       </c>
     </row>
@@ -5674,32 +5674,32 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Leprechaun'</t>
+          <t>Gaura 'Gaudi Red'</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Leprechaun'</t>
+          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the brightest foliage colour.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
+          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
+          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
+          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
         </is>
       </c>
     </row>
@@ -5711,32 +5711,32 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Winter Chocolate'</t>
+          <t>Heather 'Bell's Extra Special'</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Winter Chocolate'</t>
+          <t>Erica carnea 'Bell's Extra Special'</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
+          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
+          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
+          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
+          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Ceratostigma</t>
+          <t>Heather 'Tib'</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Ceratostigma plumbaginoides</t>
+          <t>Calluna vulgaris 'Tib'</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
+          <t>Full sun for compact growth and the best flower display.</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
+          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
+          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
+          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
         </is>
       </c>
     </row>
@@ -5785,32 +5785,32 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Hypericum (cultivar to confirm)</t>
+          <t>Bell Heather 'Providence' (2 plants)</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Hypericum (cultivar to confirm)</t>
+          <t>Daboecia cantabrica 'Providence'</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
+          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
+          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
+          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
+          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Bluebell Creeper</t>
+          <t>Heather 'Leprechaun'</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
+          <t>Calluna vulgaris 'Leprechaun'</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a warm, sheltered position.</t>
+          <t>Full sun for the brightest foliage colour.</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
+          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
+          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
+          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
         </is>
       </c>
     </row>
@@ -5859,32 +5859,32 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Rhubarb and Custard'</t>
+          <t>Heather 'Winter Chocolate'</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
+          <t>Calluna vulgaris 'Winter Chocolate'</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a warm, sheltered spot.</t>
+          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
+          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
+          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
+          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
         </is>
       </c>
     </row>
@@ -5896,32 +5896,32 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Salvia 'Salgoon Lake Blueberry'</t>
+          <t>Viola 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
+          <t>Keep evenly moist while establishing; do not allow the planting pocket to become waterlogged.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
+          <t>Deadhead faded flowers and seed pods regularly to prolong the cool-season display.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
+          <t>Purple flowers with pale picotee margins through autumn, winter and spring.</t>
         </is>
       </c>
     </row>
@@ -5933,592 +5933,814 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Fern 'Jurassic Gold'</t>
+          <t>Ceratostigma</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Dryopteris wallichiana 'Hollasic' (Jurassic Gold)</t>
+          <t>Ceratostigma plumbaginoides</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Full shade in a sheltered position.</t>
+          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Shares the existing sprinkler with location 10. Keep moist but well drained while establishing.</t>
+          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Mulch well over moist soil, keeping the crown clear. Remove dead or damaged fronds as needed and protect new croziers from late frost and slugs.</t>
+          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Rose-tinted young fronds mature through bright gold to green; deciduous to semi-evergreen depending on winter.</t>
+          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Front Stone Trough</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Hypericum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Hypericum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Part to full shade.</t>
+          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Keep moist; never bone-dry in the trough.</t>
+          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Watch for slugs/snails. Divide clumps in spring.</t>
+          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Fresh leaves spring; dies back over winter.</t>
+          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Front Box Hedge</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Wall Cotoneaster (species to confirm)</t>
+          <t>Bluebell Creeper</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Cotoneaster (species to confirm)</t>
+          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Sun to part shade.</t>
+          <t>Full sun to partial shade in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
+          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
+          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
+          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Mixed Pot</t>
+          <t>Hebe 'Rhubarb and Custard'</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Mixed seasonal planting — contents to confirm</t>
+          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
+          <t>Full sun to partial shade in a warm, sheltered spot.</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
+          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
+          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
+          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia Pot</t>
+          <t>Salvia 'Salgoon Lake Blueberry'</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia cultivars — identities to confirm</t>
+          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
+          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
+          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
+          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Apple Tree</t>
+          <t>Fern 'Jurassic Gold'</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Malus domestica</t>
+          <t>Dryopteris wallichiana 'Hollasic' (Jurassic Gold)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Full shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Water well in dry spells while fruiting.</t>
+          <t>Shares the existing sprinkler with location 10. Keep moist but well drained while establishing.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
+          <t>Mulch well over moist soil, keeping the crown clear. Remove dead or damaged fronds as needed and protect new croziers from late frost and slugs.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Blossom April–May; fruit late summer–autumn.</t>
+          <t>Rose-tinted young fronds mature through bright gold to green; deciduous to semi-evergreen depending on winter.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Front Stone Trough</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Damson Tree</t>
+          <t>Hosta</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
+          <t>Hosta</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Full sun for reliable blossom and fruit ripening.</t>
+          <t>Part to full shade.</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
+          <t>Keep moist; never bone-dry in the trough.</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
+          <t>Watch for slugs/snails. Divide clumps in spring.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
+          <t>Fresh leaves spring; dies back over winter.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Front Gate Tree</t>
+          <t>Front Box Hedge</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Weeping Crab Apple (cultivar to confirm)</t>
+          <t>Wall Cotoneaster (species to confirm)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
+          <t>Cotoneaster (species to confirm)</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
+          <t>Sun to part shade.</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
+          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
+          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
+          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Kentia Palm</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Kentia Palm — assumed</t>
+          <t>Mixed Pot</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Howea forsteriana</t>
+          <t>Mixed seasonal planting — contents to confirm</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
+          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
+          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
+          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
+          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · ‘Gioia’ Fern</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Bird’s Nest Fern ‘Gioia’</t>
+          <t>Fuchsia Pot</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Asplenium antiquum ‘Gioia’</t>
+          <t>Fuchsia cultivars — identities to confirm</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
+          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
+          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
+          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
+          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Staghorn Fern</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Staghorn Fern</t>
+          <t>Apple Tree</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Platycerium bifurcatum</t>
+          <t>Malus domestica</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
+          <t>Water well in dry spells while fruiting.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
+          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
+          <t>Blossom April–May; fruit late summer–autumn.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Cleopatra'</t>
+          <t>Damson Tree</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
+          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Full sun for reliable blossom and fruit ripening.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
+          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
+          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
+          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>Front Gate Tree</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Yellow Ripple'</t>
+          <t>Weeping Crab Apple (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
+          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Full shade to partial shade; shelter pale margins from scorching sun.</t>
+          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Share the Skimmia's evenly moist, well-drained compost; check beneath the foliage before watering.</t>
+          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Trim to keep the ivy within the pot and away from the Skimmia crown. Remove any all-green reverted shoots at their origin.</t>
+          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Evergreen lobed leaves with yellow-to-cream margins provide year-round trailing colour.</t>
+          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>House · Hallway · Kentia Palm</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Viburnum 'Lisarose'</t>
+          <t>Kentia Palm — assumed</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Viburnum tinus 'Lisarose'</t>
+          <t>Howea forsteriana</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>House · Sitting Room · ‘Gioia’ Fern</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Bird’s Nest Fern ‘Gioia’</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Asplenium antiquum ‘Gioia’</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>House · Hallway · Staghorn Fern</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Staghorn Fern</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Platycerium bifurcatum</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia Pot</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia 'Cleopatra'</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia Pot</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia 'Antarctica'</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia 'Antarctica'</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Skimmia Pot</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade.</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Keep the shared compost evenly moist but well drained.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Purple flowers with pale picotee margins through the cool season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
           <t>Viburnum Pot</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus Spirit</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus 'Anvi' (Spirit)</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sun or partial shade, with shelter from cold drying winds.</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>Pink buds open to lightly fragrant creamy-white flowers from late winter into spring, followed by blue-black ornamental berries.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G164"/>
+  <autoFilter ref="A1:G170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$165</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3861,32 +3861,32 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Trailing Fuchsia</t>
+          <t>Calluna Trio Mix (2 plants)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia (trailing cultivar)</t>
+          <t>Calluna vulgaris mixed cultivars</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to full sun.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Daily in hot weather; never let dry out completely.</t>
+          <t>Keep compost lightly moist while establishing; never waterlog.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly. Deadhead spent flowers. Not frost-hardy — replace each year.</t>
+          <t>Use free-draining, preferably ericaceous compost. Trim lightly after flowering, never into bare wood.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Pendant bicolour flowers June–October.</t>
+          <t>Evergreen foliage and late-summer to autumn colour.</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Bacopa</t>
+          <t>Viola 'Rocky Purple Picotee' (2 plants)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Sutera cordata</t>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist.</t>
+          <t>Keep compost evenly moist, particularly in windy weather.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Self-cleaning; no deadheading needed. Trim back if leggy. Tender annual.</t>
+          <t>Deadhead faded flowers and seed pods to extend the display.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Tiny white flowers May–October; neat trailing habit.</t>
+          <t>Purple flowers with a pale picotee edge through the cool season.</t>
         </is>
       </c>
     </row>
@@ -3935,32 +3935,32 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Trailing Lobelia</t>
+          <t>Hedera helix 'Yellow Ripple' (2 plants)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Lobelia erinus (trailing)</t>
+          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Shade to sun; avoid prolonged scorching sun on pale foliage.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Keep moist; hates drying out.</t>
+          <t>Keep the shared basket compost evenly moist and well drained.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Trim back mid-season if it gets straggly. Tender annual.</t>
+          <t>Trim trails to shape and keep stems clear of neighbouring crowns.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Blue trailing flowers May–October.</t>
+          <t>Evergreen variegated trails give structure through winter.</t>
         </is>
       </c>
     </row>
@@ -3972,32 +3972,32 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Trailing Verbena</t>
+          <t>Pansy 'Fire' (2 plants)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Verbena (trailing cultivar)</t>
+          <t>Viola × wittrockiana 'Fire'</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Regular; don't let dry out.</t>
+          <t>Keep evenly moist but never saturated.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to extend flowering. Tender annual.</t>
+          <t>Remove faded flowers and seed pods regularly.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Clusters of flowers June–October.</t>
+          <t>Cool-season flowers provide autumn-to-spring colour.</t>
         </is>
       </c>
     </row>
@@ -4009,661 +4009,661 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Petunia</t>
+          <t>Pansy 'Rose Surprise' (2 plants)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Petunia (cultivar unknown)</t>
+          <t>Viola × wittrockiana 'Rose Surprise'</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Check daily in warm weather; water thoroughly before the basket dries out.</t>
+          <t>Keep evenly moist but never saturated.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Feed weekly during flowering and remove faded blooms and seed capsules. Trim bare stems back to leafy growth.</t>
+          <t>Remove faded flowers and seed pods regularly.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Funnel-shaped summer flowers from June until the first frost; cultivar unresolved.</t>
+          <t>Cool-season flowers provide autumn-to-spring colour.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Front Bed 1</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Calluna Trio Mix (2 plants)</t>
+          <t>Hydrangea</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris mixed cultivars</t>
+          <t>Hydrangea macrophylla</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Morning sun, afternoon shade.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Keep compost lightly moist while establishing; never waterlog.</t>
+          <t>Thirsty — water well in dry spells.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Use free-draining, preferably ericaceous compost. Trim lightly after flowering, never into bare wood.</t>
+          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage and late-summer to autumn colour.</t>
+          <t>Mophead flowers July–Sept; bare in winter.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Front Bed 1</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Viola 'Rocky Purple Picotee' (2 plants)</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+          <t>Lavandula angustifolia</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist, particularly in windy weather.</t>
+          <t>Drought-tolerant.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded flowers and seed pods to extend the display.</t>
+          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Purple flowers with a pale picotee edge through the cool season.</t>
+          <t>Purple spikes June–Aug; aromatic year-round.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Yellow Ripple' (2 plants)</t>
+          <t>Coprosma 'Inferno'</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Hedera helix 'Golden Starlight' (Yellow Ripple)</t>
+          <t>Coprosma 'Inferno'</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Shade to sun; avoid prolonged scorching sun on pale foliage.</t>
+          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared basket compost evenly moist and well drained.</t>
+          <t>Moderate while establishing. Avoid waterlogged soil.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Trim trails to shape and keep stems clear of neighbouring crowns.</t>
+          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Evergreen variegated trails give structure through winter.</t>
+          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Pansy 'Fire' (2 plants)</t>
+          <t>Coprosma 'Pina Colada'</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Viola × wittrockiana 'Fire'</t>
+          <t>Coprosma 'Pina Colada'</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but never saturated.</t>
+          <t>Moderate while establishing. Let the soil drain between waterings.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Remove faded flowers and seed pods regularly.</t>
+          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Cool-season flowers provide autumn-to-spring colour.</t>
+          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Pansy 'Rose Surprise' (2 plants)</t>
+          <t>Coprosma 'City Knights'</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Viola × wittrockiana 'Rose Surprise'</t>
+          <t>Coprosma 'City Knights'</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but never saturated.</t>
+          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Remove faded flowers and seed pods regularly.</t>
+          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Cool-season flowers provide autumn-to-spring colour.</t>
+          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 1</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea</t>
+          <t>Hebe 'Kiwi' (Horopito)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea macrophylla</t>
+          <t>Hebe 'Kiwi'</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Morning sun, afternoon shade.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Thirsty — water well in dry spells.</t>
+          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Leave old flower heads over winter; prune to a strong bud in spring.</t>
+          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Mophead flowers July–Sept; bare in winter.</t>
+          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 1</t>
+          <t>Front Bed 2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Lavender</t>
+          <t>Polemonium 'Golden Feathers'</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Lavandula angustifolia</t>
+          <t>Polemonium 'Golden Feathers'</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Drought-tolerant.</t>
+          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Trim after flowering and again in spring; don't cut into old wood.</t>
+          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Purple spikes June–Aug; aromatic year-round.</t>
+          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Inferno'</t>
+          <t>Climbing Rose 'Super Fairy'</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Inferno'</t>
+          <t>Rosa 'Helsufair'</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; stronger light brings out the warm foliage colour.</t>
+          <t>Sun to light partial shade.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Avoid waterlogged soil.</t>
+          <t>Deep water at the base in dry spells, especially while establishing.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Shelter from cold drying winds and protect in severe frost. Trim lightly in spring to keep a compact shape.</t>
+          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Glossy green, cream, orange and red foliage intensifies in cooler weather; evergreen in a sheltered spot.</t>
+          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Pina Colada'</t>
+          <t>Variegated Dogwood</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'Pina Colada'</t>
+          <t>Cornus alba 'Elegantissima'</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; best colour in a bright, sheltered position.</t>
+          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Let the soil drain between waterings.</t>
+          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe frost and cold winds. Lightly trim any untidy growth in spring.</t>
+          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Golden foliage develops orange and bronze tones through autumn and winter; evergreen when sheltered.</t>
+          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'City Knights'</t>
+          <t>Red Hot Poker</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Coprosma 'City Knights'</t>
+          <t>Kniphofia</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; bright shelter gives the richest leaf colour.</t>
+          <t>Full sun for the strongest flowering.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing. Keep the root zone drained and do not allow prolonged drought in its first season.</t>
+          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Protect from severe frost and cold drying winds. Remove only damaged tips in spring and avoid forcing soft late growth with autumn feed.</t>
+          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage holds deep burgundy, red and dark green tones, strengthening the bed's winter colour.</t>
+          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Kiwi' (Horopito)</t>
+          <t>Leucothoe 'Little Flames'</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Kiwi'</t>
+          <t>Leucothoe 'Little Flames'</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; avoid waterlogged winter soil.</t>
+          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded spikes and trim lightly after flowering. Avoid cutting back into old bare wood.</t>
+          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Purple flower spikes in summer above glossy green leaves with dark new growth; evergreen.</t>
+          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 2</t>
+          <t>Front Bed 3</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Polemonium 'Golden Feathers'</t>
+          <t>Rose (pink)</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Polemonium 'Golden Feathers'</t>
+          <t>Rosa — IDENTIFY</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; give afternoon shade in hot weather.</t>
+          <t>Sun.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Keep evenly moist but not waterlogged while establishing.</t>
+          <t>Deep watering, mulch in spring.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Deadhead after flowering and cut tired foliage back for fresh growth. Watch for powdery mildew in dry, crowded conditions.</t>
+          <t>Prune late winter; deadhead through summer.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Gold-edged ferny foliage from spring; lilac-mauve bell flowers in spring and early summer; herbaceous in winter.</t>
+          <t>Flowers June–Sept; bare winter.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Climbing Rose 'Super Fairy'</t>
+          <t>Photinia (existing canopy)</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Helsufair'</t>
+          <t>Photinia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Sun to light partial shade.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base in dry spells, especially while establishing.</t>
+          <t>Water deeply only in prolonged dry periods once established.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Vigorous climber to about 2.5m high and 1.5m wide. Tie long shoots into the wall support and fan laterals out. Prune in late winter and deadhead after flowering.</t>
+          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Clusters of small, light-pink double flowers from June into autumn; deciduous in winter.</t>
+          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Variegated Dogwood</t>
+          <t>The Pilgrim</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Cornus alba 'Elegantissima'</t>
+          <t>Rosa 'Auswalker'</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Sun or partial shade; the leaf colour and winter stems are strongest in good light.</t>
+          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Moisture-loving. Water deeply while it re-establishes and during prolonged dry spells.</t>
+          <t>Deep water at the base during dry spells, especially while establishing.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Mulch after planting. Once settled, remove about a third of the oldest stems at the base in March to encourage vivid new winter stems.</t>
+          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Cream-edged leaves spring–autumn; brilliant red stems provide the main display in winter.</t>
+          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Red Hot Poker</t>
+          <t>The Generous Gardener</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Kniphofia</t>
+          <t>Rosa 'Ausdrawn'</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the strongest flowering.</t>
+          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Moderate while re-establishing; drought-tolerant once rooted, but dislikes winter waterlogging.</t>
+          <t>Deep water at the base during dry spells, especially in its first two years.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Keep the crown clear and well drained. Remove spent flower stems, tidy old foliage in spring and divide congested clumps every four or five years.</t>
+          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Bold orange-red poker spikes July–September above strappy, mostly evergreen foliage.</t>
+          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Leucothoe 'Little Flames'</t>
+          <t>Physocarpus Cluster 1 (2 × Little Devil + 1 × Lady in Red)</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Leucothoe 'Little Flames'</t>
+          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; some shade helps the soil stay evenly moist.</t>
+          <t>Sun to partial shade; foliage is darkest with good light.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained, especially while establishing. Use rainwater where practical.</t>
+          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Needs acidic soil. Mulch with leaf mould or composted bark and prune only to remove damaged growth or lightly reshape after flowering.</t>
+          <t>Keep all three crowns distinct, with the taller Lady in Red rising through the two compact Little Devils. Renew individual shrubs from the base only when mature and congested.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Evergreen leaves and stems flush vivid red when young, with clusters of small white urn-shaped flowers in spring.</t>
+          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 3</t>
+          <t>Front Bed 4</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Rose (pink)</t>
+          <t>Physocarpus Cluster 2 (2 × Lady in Red + 1 × Little Devil)</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Rosa — IDENTIFY</t>
+          <t>Physocarpus opulifolius 'Lady in Red' &amp; 'Little Devil'</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Sun.</t>
+          <t>Sun to partial shade; best foliage colour in brighter light.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Deep watering, mulch in spring.</t>
+          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Prune late winter; deadhead through summer.</t>
+          <t>Keep the compact Little Devil readable against the two taller Lady in Reds. Remove a few oldest stems at the base only when congestion develops.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Flowers June–Sept; bare winter.</t>
+          <t>Red, bronze and burgundy foliage spring to autumn with pink flower clusters in summer; bare in winter.</t>
         </is>
       </c>
     </row>
@@ -4675,32 +4675,32 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Photinia (existing canopy)</t>
+          <t>Azalea japonica 'Silvester'</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Photinia (cultivar to confirm)</t>
+          <t>Rhododendron 'Sylvester'</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Partial or dappled shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Water deeply only in prolonged dry periods once established.</t>
+          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Lightly prune after the spring flush if shaping is needed. Keep the new underplanting mulched and watered while it establishes around the existing roots.</t>
+          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged or wayward growth.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Evergreen canopy; fresh growth is often bronze-red and white flower clusters can appear in spring.</t>
+          <t>Compact evergreen foliage with purple-pink flowers in late spring.</t>
         </is>
       </c>
     </row>
@@ -4712,32 +4712,32 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>The Pilgrim</t>
+          <t>Nemesia 'Lady Penelope'</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Auswalker'</t>
+          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade. Aim for at least four hours of direct sun.</t>
+          <t>Full sun to light partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base during dry spells, especially while establishing.</t>
+          <t>Dropper supplied. Keep evenly moist while flowering but never waterlogged.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>David Austin medium climber. Tie new canes into the support, fanning them horizontally where possible. Feed and mulch in spring; deadhead through summer; prune in late winter.</t>
+          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Soft yellow, rosette-shaped flowers with a tea fragrance from June into autumn; deciduous in winter.</t>
+          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
         </is>
       </c>
     </row>
@@ -4749,32 +4749,32 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>The Generous Gardener</t>
+          <t>Purple Gem</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Rosa 'Ausdrawn'</t>
+          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade. Tolerates a little less sun than many climbing roses.</t>
+          <t>Shade to partial shade.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Deep water at the base during dry spells, especially in its first two years.</t>
+          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>David Austin medium climber. Train and tie in long shoots, feed and mulch in spring, deadhead repeat flowers and prune in late winter. Good disease resistance.</t>
+          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Pale pink, cup-shaped flowers fading almost white, with a strong old-rose and musk fragrance; repeat flowers June–autumn.</t>
+          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
         </is>
       </c>
     </row>
@@ -4786,32 +4786,32 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 1 (2 × Little Devil + 1 × Lady in Red)</t>
+          <t>Rhododendron 'Libretto'</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Little Devil' &amp; 'Lady in Red'</t>
+          <t>Rhododendron 'Libretto'</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; foliage is darkest with good light.</t>
+          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
+          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Keep all three crowns distinct, with the taller Lady in Red rising through the two compact Little Devils. Renew individual shrubs from the base only when mature and congested.</t>
+          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Burgundy and red-bronze foliage spring to autumn with pale pink flower clusters in early summer; bare in winter.</t>
+          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
         </is>
       </c>
     </row>
@@ -4823,32 +4823,32 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus Cluster 2 (2 × Lady in Red + 1 × Little Devil)</t>
+          <t>Festuca 'Elijah Blue' (3 plants)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Physocarpus opulifolius 'Lady in Red' &amp; 'Little Devil'</t>
+          <t>Festuca glauca 'Elijah Blue'</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade; best foliage colour in brighter light.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied. Check all three root balls through establishment and water deeply in dry spells.</t>
+          <t>Water regularly during the first season; drought tolerant once established.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Keep the compact Little Devil readable against the two taller Lady in Reds. Remove a few oldest stems at the base only when congestion develops.</t>
+          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Red, bronze and burgundy foliage spring to autumn with pink flower clusters in summer; bare in winter.</t>
+          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
         </is>
       </c>
     </row>
@@ -4860,32 +4860,32 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Azalea japonica 'Silvester'</t>
+          <t>Pieris 'Polar Passion'</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Sylvester'</t>
+          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Partial or dappled shade in a sheltered position.</t>
+          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
+          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged or wayward growth.</t>
+          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Compact evergreen foliage with purple-pink flowers in late spring.</t>
+          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
         </is>
       </c>
     </row>
@@ -4897,32 +4897,32 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Lady Penelope'</t>
+          <t>Dahlia 'Tampico'</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Nemesia 'Lady Penelope' (best-fit identification)</t>
+          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade in a sheltered position.</t>
+          <t>Full sun, sheltered from strong wind.</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep evenly moist while flowering but never waterlogged.</t>
+          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Trim tired flowering stems by about a third for another flush. Feed lightly while flowering and protect from frost.</t>
+          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Fragrant rose-pink and white flowers with pink markings and a yellow eye from late spring into autumn.</t>
+          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Purple Gem</t>
+          <t>Verbena 'Margaret's Memory'</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Sarcococca hookeriana var. humilis 'Purple Gem'</t>
+          <t>Glandularia 'Margaret's Memory'</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Shade to partial shade.</t>
+          <t>Full sun to light partial shade.</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Water in dry spells while establishing; tolerates dry shade once settled.</t>
+          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Evergreen winter-scented shrub. Keep ivy from engulfing it and prune only lightly after flowering if needed.</t>
+          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage and purple young stems; small fragrant winter flowers followed by dark berries.</t>
+          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
         </is>
       </c>
     </row>
@@ -4971,32 +4971,32 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Libretto'</t>
+          <t>Calluna Trio Mix (2 plants)</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Libretto'</t>
+          <t>Calluna vulgaris mixed cultivars</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Light dappled shade, sheltered from cold drying wind and harsh early-morning sun.</t>
+          <t>Full sun in an open position.</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Keep the shallow root zone evenly moist but never waterlogged. Prefer rainwater, especially in hard-water areas.</t>
+          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Plant shallowly in acidic, humus-rich soil. Mulch with composted bark while keeping the stem clear; deadhead carefully and prune only dead or wayward growth after flowering.</t>
+          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage all year; large dark-purple flowers with an olive-yellow flare in late May and early June.</t>
+          <t>A two-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
         </is>
       </c>
     </row>
@@ -5008,32 +5008,32 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Festuca 'Elijah Blue' (3 plants)</t>
+          <t>Achillea</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Festuca glauca 'Elijah Blue'</t>
+          <t>Achillea millefolium</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Water regularly during the first season; drought tolerant once established.</t>
+          <t>Low to moderate. Drought-tolerant once established.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Comb out dead leaves in spring and divide congested clumps every few years. Do not routinely shear hard.</t>
+          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Blue-grey, mostly evergreen foliage for year-round texture; airy flower stems in early summer.</t>
+          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
         </is>
       </c>
     </row>
@@ -5045,217 +5045,217 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Pieris 'Polar Passion'</t>
+          <t>Azalea japonica 'Lotte'</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Pieris japonica 'Ppobas' (Polar Passion)</t>
+          <t>Rhododendron 'Lotte'</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Partial shade, sheltered from cold winds and harsh early sun.</t>
+          <t>Partial or dappled shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist in acidic, well-drained soil; use rainwater where practical.</t>
+          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Mulch with ericaceous material and remove only spent flowers or damaged stems. Do not apply lime.</t>
+          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged growth.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Colourful young foliage and hanging clusters of spring flowers above evergreen leaves.</t>
+          <t>Compact glossy evergreen foliage with deep-pink flowers in late spring.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Dahlia 'Tampico'</t>
+          <t>Mexican Orange Blossom</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Dahlia Dalina Maxi Tampico ('Datretten')</t>
+          <t>Choisya ternata 'Sundance'</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Full sun, sheltered from strong wind.</t>
+          <t>Sun for best colour.</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Water deeply whenever the upper soil begins to dry; do not leave the tuber in saturated ground.</t>
+          <t>Moderate.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to keep flowers coming and support stems if they begin to lean. Lift and store the tuber frost-free after the first frost, or protect it with a deep dry mulch in a mild winter.</t>
+          <t>Light prune after flowering to shape. Low-care.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Red-and-white decorative flowers from summer until frost; dormant tuber in winter.</t>
+          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Verbena 'Margaret's Memory'</t>
+          <t>Shrub Rose (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Glandularia 'Margaret's Memory'</t>
+          <t>Rosa (Shrub Group; cultivar to confirm)</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade.</t>
+          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained while establishing; avoid waterlogged winter soil.</t>
+          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Deadhead or cut back after a flower flush. Take late-summer tip cuttings as insurance where winter cold or wet is severe.</t>
+          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Lilac-pink flowers with dark eyes from spring into late autumn; semi-evergreen in a sheltered winter.</t>
+          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Calluna Trio Mix (2 plants)</t>
+          <t>Bay Tree</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris mixed cultivars</t>
+          <t>Laurus nobilis</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Full sun in an open position.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler supplied; keep the root zone moist while establishing but never waterlogged.</t>
+          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Keep the soil acidic and free draining. Trim lightly after flowering, never back into bare old wood, and keep fallen leaves clear of the crowns.</t>
+          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>A two-plant mixed Calluna group with pink, white and lime-green flower-and-foliage interest from late summer into autumn.</t>
+          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Achillea</t>
+          <t>Japanese Skimmia</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Achillea millefolium</t>
+          <t>Skimmia japonica (cultivar and sex to confirm)</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate. Drought-tolerant once established.</t>
+          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Cut back after first flush for a second showing. Divide clumps every 2–3 years to keep vigorous. Good for cutting.</t>
+          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Flat-headed flower clusters in red, pink or yellow June–September; feathery aromatic foliage through the season.</t>
+          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 4</t>
+          <t>Front Bed 5</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Azalea japonica 'Lotte'</t>
+          <t>Hardy Fuchsia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Rhododendron 'Lotte'</t>
+          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Partial or dappled shade in a sheltered position.</t>
+          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Dropper supplied. Keep its shallow acidic root zone evenly moist, preferably with rainwater.</t>
+          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Grow shallowly in acidic, humus-rich soil and mulch with leaf mould. Deadhead carefully after flowering and prune only damaged growth.</t>
+          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Compact glossy evergreen foliage with deep-pink flowers in late spring.</t>
+          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
         </is>
       </c>
     </row>
@@ -5267,32 +5267,32 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Mexican Orange Blossom</t>
+          <t>Clematis (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Choisya ternata 'Sundance'</t>
+          <t>Clematis viticella (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Sun for best colour.</t>
+          <t>Sun to partial shade, with a cool shaded root run.</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Moderate.</t>
+          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Light prune after flowering to shape. Low-care.</t>
+          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage; scented white flowers spring &amp; again autumn.</t>
+          <t>Deciduous climber with abundant summer flowers on new growth.</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5304,32 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Shrub Rose (cultivar to confirm)</t>
+          <t>Hydrangea 'Bloody Marie'</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Rosa (Shrub Group; cultivar to confirm)</t>
+          <t>Hydrangea paniculata 'Bloody Marie'</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the strongest flowering; tolerates light partial shade.</t>
+          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Water deeply in sustained dry spells, especially while flowering and forming hips.</t>
+          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing stems in late winter. Thin congested growth and preserve sound hips where autumn colour and wildlife value are wanted.</t>
+          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Flowers are followed by red-orange rose hips — the fruits seen in the July photographs.</t>
+          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
         </is>
       </c>
     </row>
@@ -5341,32 +5341,32 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Bay Tree</t>
+          <t>Euphorbia 'Ascot Petite'</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Laurus nobilis</t>
+          <t>Euphorbia × martinii 'Ascot Petite'</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Full sun in a sheltered position.</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing and during prolonged drought; avoid waterlogged winter soil.</t>
+          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Trim lightly in late spring or summer to retain the standard shape. Remove suckers and frost-damaged tips with secateurs.</t>
+          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Aromatic evergreen leaves throughout the year; small spring flowers may be followed by dark berries on female plants.</t>
+          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Japanese Skimmia</t>
+          <t>Flaming Silver</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica (cultivar and sex to confirm)</t>
+          <t>Pieris japonica 'Flaming Silver'</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to shade; shelter from the hottest afternoon sun.</t>
+          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist but well drained, especially in dry summer weather.</t>
+          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Mulch with leaf mould or ericaceous compost and prune only to remove damaged or awkward stems. Confirm sex and cultivar from flowers and fruit.</t>
+          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Evergreen foliage and spring flower clusters; female or hermaphrodite forms can carry red berries when pollinated.</t>
+          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
         </is>
       </c>
     </row>
@@ -5415,32 +5415,32 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Hardy Fuchsia (cultivar to confirm)</t>
+          <t>Astrantia trio</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia magellanica hybrid (cultivar to confirm)</t>
+          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade, sheltered from cold drying winds.</t>
+          <t>Sun to light shade.</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Moist but well-drained soil; water in sustained dry spells while in flower.</t>
+          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Leave the top growth through winter, mulch the crown, then cut frost-damaged stems back to live buds in spring.</t>
+          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Pendant flowers from summer into autumn; top growth may die back in hard winters and regrow from the base.</t>
+          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Clematis (cultivar to confirm)</t>
+          <t>Pittosporum 'Tom Thumb'</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Clematis viticella (cultivar to confirm)</t>
+          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade, with a cool shaded root run.</t>
+          <t>Full sun to partial shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Keep moist but well drained; soak the root zone during prolonged drought.</t>
+          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Treat as pruning group 3 while the viticella identity remains the best fit: cut to strong buds 30–45cm above ground in late winter and tie in new shoots.</t>
+          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Deciduous climber with abundant summer flowers on new growth.</t>
+          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
         </is>
       </c>
     </row>
@@ -5489,32 +5489,32 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea 'Bloody Marie'</t>
+          <t>Gaura 'Gaudi Red'</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Hydrangea paniculata 'Bloody Marie'</t>
+          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; afternoon shelter helps preserve moisture.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Keep the root zone consistently moist while establishing and through hot dry spells.</t>
+          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Mulch in spring and prune in late winter or early spring before new growth, retaining a sound low framework. Panicle hydrangeas flower on the current season's shoots.</t>
+          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Large cream panicles age through pink toward red from July to September; deciduous in winter.</t>
+          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
         </is>
       </c>
     </row>
@@ -5526,32 +5526,32 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Euphorbia 'Ascot Petite'</t>
+          <t>Heather 'Bell's Extra Special'</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Euphorbia × martinii 'Ascot Petite'</t>
+          <t>Erica carnea 'Bell's Extra Special'</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a sheltered position.</t>
+          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then sparingly; sharp drainage is important in winter.</t>
+          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Remove old flowering stems at the base with gloves once replacement shoots are clear. Avoid disturbing the crown in cold wet weather.</t>
+          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Compact evergreen mound with yellow-green spring and early-summer flowerheads.</t>
+          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
         </is>
       </c>
     </row>
@@ -5563,32 +5563,32 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Flaming Silver</t>
+          <t>Heather 'Tib'</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Pieris japonica 'Flaming Silver'</t>
+          <t>Calluna vulgaris 'Tib'</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Partial shade to sun, sheltered from harsh morning frost.</t>
+          <t>Full sun for compact growth and the best flower display.</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist, especially in dry spells; do not let the rootball dry out.</t>
+          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Ericaceous shrub. Use rainwater where practical and mulch with ericaceous material; prune only lightly after flowering.</t>
+          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Evergreen, cream-edged leaves with red spring growth and cream flowers in spring.</t>
+          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
         </is>
       </c>
     </row>
@@ -5600,32 +5600,32 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Astrantia trio</t>
+          <t>Bell Heather 'Providence' (2 plants)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Astrantia major 'Buckland', 'Claret' &amp; 'Star of Love'</t>
+          <t>Daboecia cantabrica 'Providence'</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Sun to light shade.</t>
+          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Keep consistently moist during dry weather, particularly while re-establishing.</t>
+          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Mulch annually with organic matter. Deadhead to prolong flowering and cut back tired stems after flowering.</t>
+          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Pin-cushion flowers in blush, soft pink and claret shades through summer; foliage dies back in winter.</t>
+          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
         </is>
       </c>
     </row>
@@ -5637,32 +5637,32 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Pittosporum 'Tom Thumb'</t>
+          <t>Heather 'Leprechaun'</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Pittosporum tenuifolium 'Tom Thumb'</t>
+          <t>Calluna vulgaris 'Leprechaun'</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a sheltered position.</t>
+          <t>Full sun for the brightest foliage colour.</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; later only during prolonged drought. Avoid winter waterlogging.</t>
+          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Usually needs little pruning. Remove frost-damaged tips in late spring and protect from cold drying wind.</t>
+          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Lime-green young leaves mature to deep purple, forming a dense rounded evergreen mound.</t>
+          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
         </is>
       </c>
     </row>
@@ -5674,32 +5674,32 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Gaura 'Gaudi Red'</t>
+          <t>Heather 'Winter Chocolate'</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Oenothera lindheimeri 'Florgaured' (Gaudi Red)</t>
+          <t>Calluna vulgaris 'Winter Chocolate'</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then sparingly; sharp winter drainage is essential.</t>
+          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Deadhead for a longer display. Leave stems over winter and cut back after the worst frosts in spring.</t>
+          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Deep pink-red flowers dance above burgundy-green foliage from summer into autumn.</t>
+          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
         </is>
       </c>
     </row>
@@ -5711,32 +5711,32 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Bell's Extra Special'</t>
+          <t>Viola 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Erica carnea 'Bell's Extra Special'</t>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; stronger light keeps the foliage richly coloured.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then only in prolonged dry spells. Do not allow winter waterlogging.</t>
+          <t>Keep evenly moist while establishing; do not allow the planting pocket to become waterlogged.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Grow in well-drained soil. Unlike Calluna, winter heath tolerates neutral to mildly alkaline conditions. Trim lightly after flowering without cutting into bare old wood.</t>
+          <t>Deadhead faded flowers and seed pods regularly to prolong the cool-season display.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage provides year-round colour, with small heath flowers in winter and early spring.</t>
+          <t>Purple flowers with pale picotee margins through autumn, winter and spring.</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Tib'</t>
+          <t>Ceratostigma</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Tib'</t>
+          <t>Ceratostigma plumbaginoides</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Full sun for compact growth and the best flower display.</t>
+          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; afterwards it tolerates short dry spells but dislikes waterlogged soil.</t>
+          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Needs acidic, well-drained soil. Clip the faded flower spikes lightly in early spring to keep the mound compact, never cutting into bare old wood.</t>
+          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Dark evergreen foliage carries double deep-pink flower spikes from July into early autumn.</t>
+          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
         </is>
       </c>
     </row>
@@ -5785,32 +5785,32 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Bell Heather 'Providence' (2 plants)</t>
+          <t>Hypericum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Daboecia cantabrica 'Providence'</t>
+          <t>Hypericum (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a position sheltered from cold drying winds.</t>
+          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing, using rainwater where practical; avoid both drought and waterlogging.</t>
+          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Grow in acidic, humus-rich but freely drained soil. Lightly trim faded stems after flowering without cutting into old wood.</t>
+          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Evergreen mounds with comparatively large, deep rose-red bell flowers through summer and early autumn.</t>
+          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Leprechaun'</t>
+          <t>Bluebell Creeper</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Leprechaun'</t>
+          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the brightest foliage colour.</t>
+          <t>Full sun to partial shade in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; later, water only during prolonged dry spells and keep the roots well drained.</t>
+          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Plant in acidic, freely drained soil. Clip faded flower spikes lightly in spring, avoiding cuts into bare old stems.</t>
+          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>A low evergreen mound with bright lime-gold foliage, pink-tinted new growth and small late-summer flowers.</t>
+          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
         </is>
       </c>
     </row>
@@ -5859,32 +5859,32 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Heather 'Winter Chocolate'</t>
+          <t>Hebe 'Rhubarb and Custard'</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Calluna vulgaris 'Winter Chocolate'</t>
+          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Full sun to light partial shade; full sun produces the strongest foliage colour.</t>
+          <t>Full sun to partial shade in a warm, sheltered spot.</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; once rooted it tolerates short dry spells but must not sit wet.</t>
+          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Grow in acidic, well-drained soil. Lightly remove old flower spikes in March to prevent the mound becoming woody and leggy.</t>
+          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Golden foliage with pink tips in summer turns bronze and chocolate-red in winter; lavender flowers appear August–October.</t>
+          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
         </is>
       </c>
     </row>
@@ -5896,32 +5896,32 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Viola 'Rocky Purple Picotee'</t>
+          <t>Salvia 'Salgoon Lake Blueberry'</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Full sun in a warm, sheltered position.</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing; do not allow the planting pocket to become waterlogged.</t>
+          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded flowers and seed pods regularly to prolong the cool-season display.</t>
+          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Purple flowers with pale picotee margins through autumn, winter and spring.</t>
+          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
         </is>
       </c>
     </row>
@@ -5933,814 +5933,629 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Ceratostigma</t>
+          <t>Fern 'Jurassic Gold'</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Ceratostigma plumbaginoides</t>
+          <t>Dryopteris wallichiana 'Hollasic' (Jurassic Gold)</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; flowers and autumn colour are strongest in sun.</t>
+          <t>Full shade in a sheltered position.</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then only in prolonged drought. Prefers soil that drains freely.</t>
+          <t>Shares the existing sprinkler with location 10. Keep moist but well drained while establishing.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Allow room for the rhizomes to spread. Cut old top growth to the ground in spring once new shoots begin to show.</t>
+          <t>Mulch well over moist soil, keeping the crown clear. Remove dead or damaged fronds as needed and protect new croziers from late frost and slugs.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Clear cobalt-blue flowers appear from late summer into autumn as the foliage develops vivid red tints; dormant in winter.</t>
+          <t>Rose-tinted young fronds mature through bright gold to green; deciduous to semi-evergreen depending on winter.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Stone Trough</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Hypericum (cultivar to confirm)</t>
+          <t>Hosta</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Hypericum (cultivar to confirm)</t>
+          <t>Hosta</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade; more sun generally gives stronger flowering.</t>
+          <t>Part to full shade.</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing, then during prolonged dry spells only. Avoid persistently waterlogged soil.</t>
+          <t>Keep moist; never bone-dry in the trough.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Trim lightly in early spring and remove any weak or damaged stems. Confirm the cultivar from its label, flowers and berries before cultivar-specific pruning.</t>
+          <t>Watch for slugs/snails. Divide clumps in spring.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>A compact shrub grown for golden flowers with prominent stamens and, depending on cultivar, colourful ornamental berries.</t>
+          <t>Fresh leaves spring; dies back over winter.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Box Hedge</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Bluebell Creeper</t>
+          <t>Wall Cotoneaster (species to confirm)</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Billardiera heterophylla (syn. Sollya heterophylla)</t>
+          <t>Cotoneaster (species to confirm)</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a warm, sheltered position.</t>
+          <t>Sun to part shade.</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing, then water during dry spells; avoid waterlogged winter soil.</t>
+          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Tie new shoots into support and trim after flowering to control the twining growth. Protect the root area and young stems during hard frost.</t>
+          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>A slender evergreen climber with nodding blue bell flowers from summer into autumn, followed by narrow berries when pollinated.</t>
+          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Hebe 'Rhubarb and Custard'</t>
+          <t>Mixed Pot</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Veronica 'Tull 302' (Rhubarb and Custard)</t>
+          <t>Mixed seasonal planting — contents to confirm</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Full sun to partial shade in a warm, sheltered spot.</t>
+          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Moderate while establishing; drought-tolerant later, but avoid winter waterlogging.</t>
+          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Lightly trim after flowering to keep its rounded shape and protect from severe frost or cold drying winds.</t>
+          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Cream-edged grey-green leaves flush pink and rhubarb-red in cold weather; short purple flower spikes appear in mid- to late summer.</t>
+          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Pots</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Salvia 'Salgoon Lake Blueberry'</t>
+          <t>Fuchsia Pot</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Salvia 'Tl1016' (Salgoon Lake Blueberry)</t>
+          <t>Fuchsia cultivars — identities to confirm</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Full sun in a warm, sheltered position.</t>
+          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Water regularly while establishing; once rooted it has good heat and drought tolerance, provided drainage is sharp.</t>
+          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Deadhead to prolong flowering. Leave top growth over winter, mulch the crown and cut back after the worst frosts in spring; take cuttings as insurance in colder winters.</t>
+          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Compact upright growth to around 60cm with rich blueberry-purple flowers and near-black calyces from summer into autumn.</t>
+          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Front Bed 5</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Fern 'Jurassic Gold'</t>
+          <t>Apple Tree</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Dryopteris wallichiana 'Hollasic' (Jurassic Gold)</t>
+          <t>Malus domestica</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Full shade in a sheltered position.</t>
+          <t>Full sun.</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Shares the existing sprinkler with location 10. Keep moist but well drained while establishing.</t>
+          <t>Water well in dry spells while fruiting.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Mulch well over moist soil, keeping the crown clear. Remove dead or damaged fronds as needed and protect new croziers from late frost and slugs.</t>
+          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Rose-tinted young fronds mature through bright gold to green; deciduous to semi-evergreen depending on winter.</t>
+          <t>Blossom April–May; fruit late summer–autumn.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Front Stone Trough</t>
+          <t>Front Fruit Trees</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Damson Tree</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Hosta</t>
+          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Part to full shade.</t>
+          <t>Full sun for reliable blossom and fruit ripening.</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Keep moist; never bone-dry in the trough.</t>
+          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Watch for slugs/snails. Divide clumps in spring.</t>
+          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Fresh leaves spring; dies back over winter.</t>
+          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Front Box Hedge</t>
+          <t>Front Gate Tree</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Wall Cotoneaster (species to confirm)</t>
+          <t>Weeping Crab Apple (cultivar to confirm)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Cotoneaster (species to confirm)</t>
+          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Sun to part shade.</t>
+          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Water while establishing; once settled, water only in prolonged dry spells.</t>
+          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Train or lightly prune after flowering to keep growth clear of paths and masonry. Do not use box-blight or box-caterpillar treatments. Confirm the species from flowers, berries and leaf undersides.</t>
+          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Small leaves on herringbone stems; flowers in late spring or summer followed by red berries. Evergreen or semi-evergreen depending on species and winter.</t>
+          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>House · Hallway · Kentia Palm</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Mixed Pot</t>
+          <t>Kentia Palm — assumed</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Mixed seasonal planting — contents to confirm</t>
+          <t>Howea forsteriana</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Bright outdoor position; confirm the needs of each constituent plant when identified.</t>
+          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Check the compost frequently in warm or windy weather; supplied by an adjustable sprinkler.</t>
+          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Deadhead finished flowers, keep the drainage holes clear and record the individual plants and cultivars as labels or clearer photographs become available.</t>
+          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>A mixed seasonal container providing varied flower colour; exact contents remain unresolved.</t>
+          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Front Pots</t>
+          <t>House · Sitting Room · ‘Gioia’ Fern</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia Pot</t>
+          <t>Bird’s Nest Fern ‘Gioia’</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Fuchsia cultivars — identities to confirm</t>
+          <t>Asplenium antiquum ‘Gioia’</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Bright light or partial shade, protected from the harshest reflected afternoon heat.</t>
+          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Keep the compost evenly moist but freely drained; supplied by an adjustable sprinkler.</t>
+          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Deadhead for continued flowering, check the sprinkler reaches the compost rather than only the foliage, and confirm whether the plants are hardy before winter.</t>
+          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Pendant Fuchsia flowers through summer and autumn; exact cultivars and winter hardiness remain unresolved.</t>
+          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>House · Hallway · Staghorn Fern</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Apple Tree</t>
+          <t>Staghorn Fern</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Malus domestica</t>
+          <t>Platycerium bifurcatum</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Full sun.</t>
+          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Water well in dry spells while fruiting.</t>
+          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Winter prune for shape and airflow; thin fruit in June if heavy.</t>
+          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Blossom April–May; fruit late summer–autumn.</t>
+          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Front Fruit Trees</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Damson Tree</t>
+          <t>Skimmia 'Cleopatra'</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Prunus domestica subsp. insititia (cultivar to confirm)</t>
+          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Full sun for reliable blossom and fruit ripening.</t>
+          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged dry spells, especially from fruit set to harvest.</t>
+          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Prune only in dry summer weather to reduce silver-leaf and canker risk; remove suckers from below the graft.</t>
+          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>White spring blossom followed by blue-black damsons in late summer or early autumn.</t>
+          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Front Gate Tree</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Weeping Crab Apple (cultivar to confirm)</t>
+          <t>Skimmia 'Antarctica'</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Malus (weeping cultivar; 'Red Jade' is a best-fit possibility)</t>
+          <t>Skimmia 'Antarctica'</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Full sun for the best blossom, fruit colour and balanced growth.</t>
+          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Water deeply during prolonged drought, particularly while establishing and while fruit is swelling.</t>
+          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Remove dead, damaged and crossing wood in winter, preserving the natural weeping framework. Record blossom and ripe-fruit details before naming the cultivar.</t>
+          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Spring blossom followed by small ornamental crab apples that can persist into autumn and winter.</t>
+          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Kentia Palm</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Kentia Palm — assumed</t>
+          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Howea forsteriana</t>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Bright indirect light; protect the fronds from strong direct sun.</t>
+          <t>Sun to partial shade.</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Check the upper few centimetres of compost before watering, then drain fully and empty the white cachepot.</t>
+          <t>Keep the shared compost evenly moist but well drained.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity, keep away from cold draughts and radiators, and feed monthly during active spring and summer growth.</t>
+          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows as light levels fall in winter.</t>
+          <t>Purple flowers with pale picotee margins through the cool season.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · ‘Gioia’ Fern</t>
+          <t>Bed 2/3 Wall Pot</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Bird’s Nest Fern ‘Gioia’</t>
+          <t>Viburnum 'Lisarose'</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Asplenium antiquum ‘Gioia’</t>
+          <t>Viburnum tinus 'Lisarose'</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Bright, indirect light; protect the fronds from direct sun through the glass.</t>
+          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Keep compost lightly moist but never saturated; water around the pot edge rather than into the centre rosette.</t>
+          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Give it steady warmth and higher humidity, removing only damaged fronds at the base.</t>
+          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Evergreen indoor foliage throughout the year; growth slows in lower winter light.</t>
+          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>House · Hallway · Staghorn Fern</t>
+          <t>Bed 2/3 Wall Pot</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Staghorn Fern</t>
+          <t>Vinca minor 'Illumination'</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Platycerium bifurcatum</t>
+          <t>Vinca minor 'Illumination'</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Bright, indirect light; avoid harsh midday sun and cold draughts.</t>
+          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Check the growing medium before watering and let excess water drain completely; never keep the base wet.</t>
+          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Maintain moderate humidity and keep the fern clear of direct radiator heat. Leave the brown papery shield fronds in place.</t>
+          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Evergreen antler-like fronds are the display throughout the year; growth is slower in winter.</t>
+          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>Viburnum Pot</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Cleopatra'</t>
+          <t>Viburnum tinus Spirit</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
+          <t>Viburnum tinus 'Anvi' (Spirit)</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Sun or partial shade, with shelter from cold drying winds.</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
+          <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
+          <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Skimmia Pot</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>Skimmia 'Antarctica'</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Skimmia 'Antarctica'</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Skimmia Pot</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Viola cornuta 'Rocky Purple Picotee'</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Sun to partial shade.</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>Keep the shared compost evenly moist but well drained.</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>Purple flowers with pale picotee margins through the cool season.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Bed 2/3 Wall Pot</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>Viburnum 'Lisarose'</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Viburnum tinus 'Lisarose'</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>Bed 2/3 Wall Pot</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>Vinca minor 'Illumination'</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Vinca minor 'Illumination'</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>Viburnum Pot</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>Viburnum tinus Spirit</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Viburnum tinus 'Anvi' (Spirit)</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>Sun or partial shade, with shelter from cold drying winds.</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
           <t>Pink buds open to lightly fragrant creamy-white flowers from late winter into spring, followed by blue-black ornamental berries.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G170"/>
+  <autoFilter ref="A1:G165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/Oak_Lodge_Garden_Plant_Guide.xlsx
+++ b/Oak_Lodge_Garden_Plant_Guide.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant Guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant Guide'!$A$1:$G$168</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Plant Guide'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6261,7 +6261,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>House · Sitting Room · ‘Gioia’ Fern</t>
+          <t>House · Kitchen / Dining · ‘Gioia’ Fern</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -6335,227 +6335,338 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>House · Sitting Room · Shared Pot · Spider Plant</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Cleopatra'</t>
+          <t>Spider Plant ‘Vittatum’ — assumed</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
+          <t>Chlorophytum comosum ‘Vittatum’</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Bright indirect light is ideal; it tolerates lower light but direct hot sun can scorch the striped leaves.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
+          <t>Allow the compost surface to begin drying, then water thoroughly and let the shared container drain fully.</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
+          <t>Trim only spent stems or badly damaged leaves, feed lightly during active growth and root the hanging plantlets if wanted.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
+          <t>Evergreen striped foliage and hanging plantlets are the year-round display; growth slows in winter.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>House · Sitting Room · Shared Pot · Parlour Palm</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Antarctica'</t>
+          <t>Parlour Palm — assumed</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Skimmia 'Antarctica'</t>
+          <t>Chamaedorea elegans</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
+          <t>Bright indirect light or light shade; protect the fine leaflets from strong direct sun.</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
+          <t>Check below the surface before watering; keep lightly moist in growth but never leave the shared planter waterlogged.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
+          <t>Keep warm, remove only fully brown fronds at the base and feed monthly at low strength in spring and summer.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
+          <t>Evergreen fine-textured fronds provide the display throughout the year; growth is slowest in winter.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Skimmia Pot</t>
+          <t>House · Sitting Room · Shared Pot · Arrowhead Vine</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
+          <t>Arrowhead Vine — assumed</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+          <t>Syngonium podophyllum</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Sun to partial shade.</t>
+          <t>Bright indirect light; keep the leaves out of strong direct sun through the glass.</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Keep the shared compost evenly moist but well drained.</t>
+          <t>Keep lightly moist during active growth, allowing the surface to begin drying; water more sparingly in winter.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
+          <t>Guide or trim lengthening stems in spring, feed during active growth and wear gloves if pruning because the sap is irritating.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Purple flowers with pale picotee margins through the cool season.</t>
+          <t>Evergreen juvenile arrow-shaped leaves become more divided as stems mature; indoor flowering is uncommon.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Viburnum 'Lisarose'</t>
+          <t>Skimmia 'Cleopatra'</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Viburnum tinus 'Lisarose'</t>
+          <t>Skimmia japonica 'Snep24' (Cleopatra)</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+          <t>Light to full shade, sheltered from harsh sun and drying wind.</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+          <t>Keep the shared compost consistently moist but well drained, preferably using rainwater.</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+          <t>Mulch or top-dress with leaf mould or ericaceous compost. Prune only lightly after flowering and keep ivy stems away from its crown.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+          <t>Glossy evergreen foliage, fragrant ivory spring flowers and long-lasting red berries from autumn into winter.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Bed 2/3 Wall Pot</t>
+          <t>Skimmia Pot</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Skimmia 'Antarctica'</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Vinca minor 'Illumination'</t>
+          <t>Skimmia 'Antarctica'</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+          <t>Partial to full shade, sheltered from harsh sun and drying wind.</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+          <t>Keep compost evenly moist and freely drained; rainwater is preferred where practical.</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+          <t>Use ericaceous compost and prune only lightly after flowering. Do not let the root ball dry out while establishing.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+          <t>Glossy evergreen foliage and spring flower buds give year-round structure.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>Skimmia Pot</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Viola 'Rocky Purple Picotee' (3 plants)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Viola cornuta 'Rocky Purple Picotee'</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Sun to partial shade.</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Keep the shared compost evenly moist but well drained.</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Deadhead faded flowers and seed pods regularly to prolong flowering.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Purple flowers with pale picotee margins through the cool season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Viburnum tinus 'Lisarose'</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Sun, partial shade or shade, sheltered from cold drying winds.</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Keep evenly moist while establishing; never leave the container waterlogged.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Use humus-rich, well-drained compost. Prune only after flowering if its size needs controlling.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Brick-red winter buds open to pink-and-white flowers, followed by dark blue ornamental berries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Bed 2/3 Wall Pot</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Vinca minor 'Illumination'</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Sun to shade; foliage colours best in bright indirect light or partial shade.</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Moderate. Let the surface dry slightly without allowing the pot to dry completely.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Trim trailing stems to shape and keep drainage holes clear. Do not plant into open ground without a spread plan.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Golden evergreen foliage with narrow green margins and violet-blue flowers from spring into autumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
           <t>Viburnum Pot</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus Spirit</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>Viburnum tinus 'Anvi' (Spirit)</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sun or partial shade, with shelter from cold drying winds.</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Keep evenly moist but well drained while establishing; check the pot through dry and windy weather.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Prune only after flowering if needed. Refresh the top compost in spring and protect the container during prolonged severe cold.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>Pink buds open to lightly fragrant creamy-white flowers from late winter into spring, followed by blue-black ornamental berries.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G165"/>
+  <autoFilter ref="A1:G168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
